--- a/yello_doctor_sharjah.xlsx
+++ b/yello_doctor_sharjah.xlsx
@@ -46,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -428,7 +427,7 @@
           <t>Address</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
@@ -455,16 +454,12 @@
           <t>Block A Buheira Corniche Road - Al Majaz 3 - Al Majaz, Sharjah , UAE</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>+971 6 565 0690</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.com</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>'+971 6 565 0690</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/344092/al-abqari-dental-clinic</t>
@@ -482,16 +477,12 @@
           <t>BM Towers, Office No:106, Near Ansar Mall, Sharjah , UAE</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>+971 6 561 7822 2015</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.com</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>'+971 6 561 7822</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/351899/austin-center-for-rehabilitation-of-person-with-disabilities</t>
@@ -509,16 +500,12 @@
           <t>Al Sharqan-Extension, Al Arouba Street, Al Heera Suburb, Towards Ajman, Sharjah , UAE</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>+971 6 566 7996 2016</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.com</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>'+971 6 566 7996</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/354307/sunny-sharqan-medical-centre</t>
@@ -536,16 +523,12 @@
           <t>Al Tawoos Building,Shop # 3, King Abdul Aziz Road(Immigration Road), OPP Emirates NBD, Al Mahatah, Sharjah , UAE</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>+971 6 559 0007 2016</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.com</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>'+971 6 559 0007</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/352212/al-afdal-medical-center</t>
@@ -563,16 +546,12 @@
           <t>Near Istanbul Supermarket, Al Majaz-3, Sharjah , UAE</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>+971 6 525 3756 2016</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.com</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>'+971 6 525 3756</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/356351/mulk-physiotherapy-center</t>
@@ -590,16 +569,12 @@
           <t>Flat 106 AlHussaini Bldg, Behind University City Road, Near University City, Muwaileh Commercial area, Behind Muwaileh Hyper Market, , Sharjah , UAE</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>+971 6 550 3558 2013</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.com</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>'+971 6 550 3558</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/343954/ibtisamty-dental-clinic</t>
@@ -617,16 +592,12 @@
           <t>P.O Box: 62236 Near Musalla Park, Rolla, Sharjah -UAE</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>+971 6 521 8889 2016</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.com</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>'+971 6 521 8889</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/374124/shifa-al-jazeera-medical-centre-llc</t>
@@ -644,16 +615,12 @@
           <t>Al Zahraa Street, Al Nasserya, Sharjah , UAE</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>+971 6 506 0000 1992</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.com</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>'+971 6 506 0000</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/17710/zulekha-hospital</t>
@@ -671,16 +638,12 @@
           <t>Flat# 103, 1St Floor, Noor Building, Al Sharq st, Al Nabaah Area Po box 79279, Sharjah , UAE</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>+971 6 566 7661 2015</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.com</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>'+971 6 566 7661</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/352120/dr-uma-maheswari</t>
@@ -698,16 +661,12 @@
           <t>Maysaloon, Sharjah , UAE</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>+971 6 559 1985 2014</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.com</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>'+971 6 559 1985</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/349515/al-elaj-medical-equipment-tr</t>
@@ -725,16 +684,12 @@
           <t>AL Taawun street Emirates tower, Sharjah , UAE</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>+971 6 526 6885 2012</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.com</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>'+971 6 526 6885</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/347642/art-medical-center</t>
@@ -752,16 +707,12 @@
           <t>PO BOX 77399, J Mart Building, First Floor, Opp. Police Headquarters, Al-Zahra Street, Sharjah UAE.</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>+971 6 568 8600 2017</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.com</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>'+971 6 568 8600</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/358083/asala-medical-center</t>
@@ -779,16 +730,12 @@
           <t>Flat 101 Above Al Rostamani Exchange Bldgs, Opposite Manama Supermarket Al Arouba Street, Near KM Trading Rolla, Sharjah , UAE</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>+971 6 567 1707</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.com</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>'+971 6 567 1707</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/347083/al-bawadi-medicaldiagnostic-center</t>
@@ -806,16 +753,12 @@
           <t>1ST Floor, Saleh Bin Saleh Bldg. King Faisal Street, Behind EMAX Electronics Store/ Grand Excelsior Hotel Near Prime Tower Hotel P.O. BOX 80457, SHARJ, Sharjah , UAE</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>+971 6 555 1575 2005</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.com</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>'+971 6 555 1575</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/355131/right-medical-centre</t>
@@ -833,16 +776,12 @@
           <t>Rolla Tower, Flat 303/304, Al Zahra Street, Al Ghuwair, Sharjah , UAE</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>+971 6 561 2737 1992</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.com</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>'+971 6 561 2737</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18028/abrahams-medical-centre</t>
@@ -860,16 +799,12 @@
           <t>102, al wazir building ,opposite Qantra restaurant, Sharjah , UAE</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>+971 6 530 6161 2012</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.com</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>'+971 6 530 6161</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/362487/ahlan-medical-center</t>
@@ -887,16 +822,12 @@
           <t>Lifeline Clinic، City Tower - Office 11 1st Floor - Bu Shaghara, Sharjah , UAE</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
-        <is>
-          <t>+971 6 553 0557</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.com</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>'+971 6 553 0557</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18451/dr-ashok-menon-clinic</t>
@@ -914,16 +845,12 @@
           <t>Al Sharq - Maysaloon, Sharjah , UAE</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
-        <is>
-          <t>+971 6 574 4529</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.com</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>'+971 6 574 4529</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18042/ahalia-medical-centre</t>
@@ -941,16 +868,12 @@
           <t>Sheikh Faisal Al Qassemi Bldg, Block B, Floor 1, Suite 1113-116, Maliha Road, Industrial Area 15, Sharjah , UAE</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>1113-116</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.com</t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>'+971 6 535 3582</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/342387/al-shams-medicaldiagnostic-centre</t>
@@ -968,19 +891,7872 @@
           <t>Airport International Free Zone, Sharjah , UAE</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>+971 6 557 1132 1992</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.com</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>'+971 6 557 1132</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/207709/bentham-science-publishers-ltd-fzc</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Bissam Medical Centre</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Buhariah Corniche.Golden Tower.1st Floor, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>'+971 6 573 7005</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153264/bissam-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>California Dental CLinic</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Buhaira Corniche- crystal plaza- clock C- office 1003, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>'+971 6 522 4422</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/359495/california-dental-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Class Medical Centre</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Al Saud Tower, Al Arouba Street,Al Mujarrah, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>'+971 6 565 2332</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18370/class-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Prime Medical Center - Sharjah</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>King Abdul Aziz Road, Al Nud, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>'+971 6 575 2200</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18924/prime-medical-center-sharjah</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Yathish Kamath, Dr - Mds (marina Medical Centre)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>M Flr, Opp Rotana Hotel, Al Arouba St, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>'+971 6 562 5234</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153395/yathish-kamath-dr-mds-marina-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Abubakr Medical Center</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Suite No. 107, 108, First Floor, Al Khudira Building, Al Zahra Street, Rolla, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>'+971 6 562 3151</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18032/abubakr-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Adam Veterinary Medicines L.L.C</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>'+971 50 424 9032</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/367437/adam-veterinary-medicines-llc</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Al Khajah Medical Center</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Al Fardan Center, 2nd Floor, Office No. A-201, on Cornish Al Buhaira Street on Khalid Lagoon, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>'+971 6 556 2200</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/222958/al-khaja-medical-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Al Saha Al Shifa</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Rolla Mall,City of Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>'+971 6 563 2618</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/361038/al-saha-al-shifa</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Bhatia Medical Centre</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Al Arouba St, Bank Street - Al Shuwaiheen , Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>'+971 6 575 3888</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/17647/bhatia-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Doctors Medical Centre</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ADCB Building - 6th Floor - Meena Road - near Central Post Office , Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>'+971 6 563 2100</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18416/doctors-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Dr Zain's Homeopathic Clinic, Sharjah</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1st Floor, Business Link Building,Opp: Sharjah Co Op Society - Al Khalidia St - Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>'+971 52 277 5005</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/364544/dr-zains-homeopathic-clinic-sharjah</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Elite Medical Center</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Villa 49, Al Meena Street, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>'+971 6 530 9898</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/367702/elite-medical-center</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Ishaq Bin Omran Medical Center (IBO)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Sheikh Salem Al Qassimi Street Al Qarayen, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>'+971 6 518 0800</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/362215/ishaq-bin-omran-medical-center-ibo</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Oriana Hospital</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Manazil Tower 2 – New Al Taawun Rd – Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>'+971 6 525 1000</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/347798/oriana-hospital</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Venniyil Medical Centre</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Land and Sea House hold shop building, Near Corniche Post Office, Old Iranian Market, Al Suwaihean, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>'+971 6 568 2258</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/25748/venniyil-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Al Kanary Medical Clinic</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Muwaileh Commercial - Industrial Area , Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>'+971 6 534 4439</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18143/al-kanary-medical-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>University Hospital Sharjah</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Sharjah University City, UAE</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>'+971 6 505 7048</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/341538/university-hospital-sharjah</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hygiene Fresh</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Food Court Gate No - 3 - Saif Zone - Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>'+971 600520057</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/371303/hygiene-fresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Al Amumah Medical Center</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Flot# 103, 1St Floor, Noor Building Al Sharq st, Al Nabaah Area Po box 79279, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>'+971 6 566 7661</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/352098/al-amumah-medical-center</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Lifeway Specialized Medical Centre</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BIN HAM BUILDING, TOWER-A 105 FLAT AL MAMZAR AREA OPPOSITE ANSAR MALL , SHARJAH , UAE</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>'+971 6 530 4900</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/353173/lifeway-specialized-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Nahar Mampilly Medical Centre</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>'+971 6 566 8745</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18875/nahar-mampilly-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unipex Dairy Products Co. Ltd</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Industrial Area 2 - Industrial Area, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>'+971 6 533 7864</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/148789/unipex-dairy-products-co-ltd</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Al Durrah Radiology Center</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Al Durrah Tower, Next to Al Buhaira Police Station, First Floor, Corniche Al Buhaira, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>'+971 6 556 9888</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/350245/al-durrah-radiology-center</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Al Watania Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Al Mina Road, Al Jubail, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>'+971 6 569 1791</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/19188/al-watania-veterinary-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Al Ysra Medical Center</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1st FLOOR, Hamad Khabid Building Ammar Ibn Yasir Mosque R/A, Al Dhaid, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>'+971 6 882 2270</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/349667/al-ysra-medical-center</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Cosme Surge</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>'+971 6 524 5444</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18380/cosme-surge</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Europets Hospital</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Villa 341,Mirgab Street, Al Quadsia, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>'+971 50 860 6857</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/19201/europets-hospital</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Grade Refrigeration LLC</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Opposite Marwan Cont Co, Industrial Area 15, P.O. Box: 69619, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>'+971 6 534 3803</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/319890/grade-refrigeration-llc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Gulf Medical Projects</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Al Hind Tower - AL Khan Corniche St - Al Khan - Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>'+971 6 509 5555</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/371813/gulf-medical-projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>IBO</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Sheikh Salem Al Qassimi Street  Al Qarayen, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>'+971 6 518 0800</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/360000/ibo</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Lifeway Specialized Medical Centre</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>105, Al Bin Ham Building, Al Mamzar, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>'+971 6 530 4900</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/366850/lifeway-specialized-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Best gynaecologist in uae</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Al Durra Tower– 8th Floor – Clinic No. 806 Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>'+971 50 963 8577</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/361312/best-gynaecologist-in-uae</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>International Radiology Centre</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Crystal Plaza building, Buhairah Corniche, P.O. Box: 26366, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>'+971 6 573 8088</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/333177/international-radiology-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>New Hope IVF</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>New Hope IVF AL SONDUS TOWER. , AL MAMZAR CORNICHE,, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>'+971 6 525 4446</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/362584/new-hope-ivf</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Al Amanah Medical Centre</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Al Mubarak Centre, Floor 3, Office 308,Al Arouba Street, Al Naba'ah, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>'+971 6 561 5545</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18070/al-amanah-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Al Mahmood Medical Centre</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Al Zahra Street, Al Mussalla, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>'+971 6 561 7277</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18155/al-mahmood-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Al Salam Clinic</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Al Arouba Street, Al Ghuwair, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>'+971 6 561 4262</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18224/al-salam-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Al Sherouq Medical Center</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Orient Building, Rolla - 1St Floor - Al Arouba St - Sharjah - United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>'+971 50 252 5966</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/373035/al-sherouq-medical-center</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Al Safwa Radiology Center</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>3rd Floor,Tower C, Al Marzouqi Towers (CG Mall), King Faisal Street, Al Nud, Al Qasimia, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>'+971 6 556 3969</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/373835/al-safwa-radiology-center</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Central Private Hospital</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Sheikh Zayed Road, Maysaloon, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>'+971 6 563 6308</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/17650/central-private-hospital</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Desert Mart</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Sharjah fze, UAE</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>'+971 56 563 6802</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/357446/desert-mart</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Emirates Private Poly Clinic</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Bin Omair Street, Abu Shagara, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>'+971 6 555 1666</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18635/emirates-private-poly-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Eve Fertility Center</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Corniche Al Buhaira, Al Nakheel Tower 303, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>'+971 6 572 5551</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/365301/eve-fertility-center</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>French Rheumatism Clinic</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Buhaira Building, Corniche Street,Al Majaz 1, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>'+971 6 574 4266</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18661/french-rheumatism-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Gynaecologist in sharjah</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Al Durra Tower – next to Al FardanCenter – 8th Floor – Clinic No. 806, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>'+971 50 963 8577</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/363115/gynaecologist-in-sharjah</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Julphar  Drug Store  Sharjah</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Po Box 997, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>'+971 6 539 4466</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/241300/julphar-drug-store-sharjah</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Medical center in sharjah</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Majestic Tower, 1, Al Taawun Street, S Floor, Office 701, Al Ta’awun, Al Khalidiah, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>'+971 6 565 2929</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/360495/medical-center-in-sharjah</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Minal Medical Clinic</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Crystal Plaza, Corniche Street,Al Majaz 1, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>'+971 6 574 9610</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18850/minal-medical-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Nathani Medical Centre</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Arabian Gulf Street, Al Shuwaiheen, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>'+971 6 568 6200</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18880/nathani-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>New Medical Centre</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>King Faisal Street, Al Majaz 2, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>'+971 6 553 6936</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18896/new-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Reem Specialists Medical Centre</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Al Arouba Street, Al Ghuwair, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>'+971 6 562 5422</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18943/reem-specialists-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Royal Hospital</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Airport Road, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>'+971 6 558 1515</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/17691/royal-hospital</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Sharjah Corniche Hospital</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Corniche Plaza 2,Al Buhairah Corniche Road, Al Majaz 1, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>'+971 6 575 1222</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/17696/sharjah-corniche-hospital</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Solanki Dental Center</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Mubarak Centre, Office 312,Al Arouba Street, Al Naba'ah, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>'+971 6 561 6556</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/19000/solanki-dental-center</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Ahlan Dental Clinic</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Al Nahda Street, Al Nahda, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>'+971 6 530 5882</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18047/ahlan-dental-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Dr Ramzi Assi Dental Clinic</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>King Faisal Street, Al Majaz 1, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>'+971 6 555 1981</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18555/dr-ramzi-assi-dental-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Al Ain Farms For Livestock Production</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Saif Zone, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>'+971 6 557 0722</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/147645/al-ain-farms-for-livestock-production</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Optimum Medical Center</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>804C, Crystal Plaza, Buhaira Corniche, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>'+971 6 561 3030</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/348714/optimum-medical-center</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Derma &amp; Health</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>'+971 4 323 1889</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/371138/dermahealth</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Jwan Murad</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Barjeel Hospital- Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18770/jwan-murad-fertility-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Abdul Ghani Siddique Ent Clinic, Dr</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>'+971 6 556 2727</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/152772/abdul-ghani-siddique-ent-clinic-dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Al Ahalia Regional Medical Centre</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Ibrahim Mohammed Al Midfaa Street, Al Mussalla, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>'+971 6 562 1700</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18057/al-ahalia-regional-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Al Buhairah Medical Centre</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Jamal Abdul Nasser Street, Al Majaz 2, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>'+971 6 559 9699</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18089/al-buhairah-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Al Faseel Veterinary &amp; Pet Clinic</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Al Khan Steet, Al Majaz, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>'+971 6 559 9147</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/19179/al-faseel-veterinarypet-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Al Jahharah Dental Clinic</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Arabian Gulf Street, Al Ghuwair, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>'+971 6 562 4456</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18130/al-jahharah-dental-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Alpha Medical Centre</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Al Ghuwair Tower,Al Arouba Street, Al Ghuwair, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>'+971 6 561 7577</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18280/alpha-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>AL Thiqah Club for Handicapped</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Po Box 4788, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>'+971 6 538 9999</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/228848/al-thiqah-club-for-handicapped</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Annie Dental Clinic</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Al Jabiri Building, Apt 104,Abu Shagara, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>'+971 6 559 4454</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18296/annie-dental-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Aqsa International Fzc</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Dubai, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>'+971 6 557 3559</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/147655/aqsa-international-fzc</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Best Physiotherapy clinic in sharjah</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>CURE MEDICAL CENTER PHYSIOTHERAPY ASAS Tower, Office Entrance, 2nd Floor,202  In Front Of Al Bareej, Al Khan Corniche  Street,P.O: 22370 Sharjah -UAE</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>'+971 6 530 3999</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/361501/best-physiotherapy-clinic-in-sharjah</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Dablan Dental Clinic</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Al Khaja Building, Al Wahda Street,Al Majaz 2, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>'+971 6 559 2930</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18388/dablan-dental-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Dr Ali Salem Hindi Clinic</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Al Thuraya Building,Al Wahda Street, Bu Danig, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>'+971 6 574 6006</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18437/dr-ali-salem-hindi-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Dr Asad I Dajani Specialized Centre</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Corniche Plaza 2, Corniche Street,Al Majaz 1, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>'+971 6 572 7700</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18449/dr-asad-i-dajani-specialized-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Dr Gayatree Medical Centre</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>King Faisal Street, Al Majaz 2, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>'+971 6 559 1110</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18464/dr-gayatree-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Dr Habib Ear Nose &amp; Throat Clinic</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Corniche Plaza 2, Corniche Street,Al Majaz 1, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>'+971 6 572 7767</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18469/dr-habib-ear-nosethroat-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Dr Hijazi's Clinic</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Al Zahra Street, Al Ghuwair, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>'+971 6 563 5029</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18475/dr-hijazis-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Dr Mandar Medical Clinic</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Corniche Street, Al Majaz 1, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>'+971 6 568 5557</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18513/dr-mandar-medical-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Dr Nemat Mossalami</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Al Wahda Street, opposite to new gold center, Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>'+971 6 572 1052</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18546/dr-nemat-mossalami</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Dr Samir Abou Zeid Clinic</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Burj Al Awael Building, Jamal Abdul Nasser Street,Al Majaz 2, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>'+971 6 553 7007</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18575/dr-samir-abou-zeid-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Dr Suha Al Farhan Clinic</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Corniche Plaza 2, Corniche Street,Al Majaz 1, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>'+971 6 573 7242</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18590/dr-suha-al-farhan-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Dr Sunny Medical Centre</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Al Wasit Street, Al Shahba, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>'+971 6 563 9966</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18592/dr-sunny-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Ideal Medical Centre</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Al Arouba Street, Al Ghuwair, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>'+971 6 562 3844</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18740/ideal-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Indulekha Medical Clinic</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Al Wahda Street, Al Majaz 2, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>'+971 6 559 5285</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18746/indulekha-medical-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Jennifer Skin Care Centre</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>'+971 6 524 2688</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18762/jennifer-skin-care-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Mampilly Eye Clinic</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Al Arouba Street, Al Ghuwair, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>'+971 6 561 6464</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18810/mampilly-eye-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Marijeh Clinic</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Al Maraija Street, Al Jubail, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>'+971 6 569 1400</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18817/marijeh-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Marina Medical Centre</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Dafco Building, Al Mussalla, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>'+971 6 562 5234</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18819/marina-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Medical House for Diagnosis &amp; Treatment</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Al Zahra St, Maysaloon, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>'+971 6 563 7719</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18831/medical-house-for-diagnosistreatment</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Medicare Clinic</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Al Arouba Street, Al Ghuwair, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>'+971 6 562 6922</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18836/medicare-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Mega Medical Centre</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Al Wahda St, Industrial Area 1, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>'+971 6 539 6200</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18841/mega-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Modern Dental Clinic</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Al Muheiri Building, Apt 111,Al Wahda St, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>'+971 6 533 9799</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18855/modern-dental-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Roy Dental Clinic</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Al Owais Building, Al Arouba Street,Umm Tarrafa, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>'+971 6 561 5111</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18954/roy-dental-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Russian Medical &amp; Scientific Complex</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Al Wahda Street, Al Majaz 2, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>'+971 6 555 3355</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18962/russian-medicalscientific-complex</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Sara Medical Centre</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Sara Tower, Al Majaz 3, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>'+971 6 556 8888</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18976/sara-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Shamma Dental Clinic</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Jamal Abdul Nasser Street, Al Majaz 2, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>'+971 6 553 1080</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18986/shamma-dental-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Sunny Al Nahda Medical Centre</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Al Shaiba Bldg, Floor 1, Flat 115, Al Nahda, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>'+971 6 530 5252</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/342444/sunny-al-nahda-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Sunny Speciality Medical Center</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Habib Bank AG Zurich Bldg, Floor 0, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>'+971 55 390 8860</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/342445/sunny-speciality-medical-center</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Venniyil Medical Centre</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Corniche Street, Al Shuwaiheen, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>'+971 6 568 2258</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/19049/venniyil-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Ziad E Baghdan Clinic</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Abu Ghazala Building, Al Wahda Street,Industrial Area 1, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>'+971 6 533 3949</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/19070/ziad-e-baghdan-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Cure Medical Center Physiotherapy</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>ASAS Tower, Office Entrance, 2nd Floor,202  In Front Of Al Bareej, Al Khan Corniche  Street,P.O: 22370 Sharjah -UAE</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>'+971 6 530 3999</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/363079/cure-medical-center-physiotherapy</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Kuwaiti Hospital</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Al Qadasia, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>'+971 6 524 2111</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/17673/kuwaiti-hospital</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Yalla Doc</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>'+971 55 551 2478</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/369118/yalla-doc</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Al Mueed Medical Centre L.L.C.</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Arabian Gulf Street, Al Nabba, Sharjah Clock Tower Area, United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>'+971 6 563 1429</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18173/al-mueed-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Al Zahra Private Hospital</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Al Ghuwair, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>'+971 6 561 9999</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/17640/al-zahra-private-hospital</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>CPR Select</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>44184, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/317241/cpr-select</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Niyana</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/368316/niyana</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Abrahams Medical Clinic</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>'+971 6 561 2737</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153514/abrahams-medical-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Al Faiez Medical Clinic</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Howaidhen Building, Floor 1, Flats 101-104, Hatta Road, Al Madam, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>'+971 6 886 1202</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/342379/al-faiez-medical-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Al Mahmoud Medical Centre</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>'+971 6 561 7277</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/152788/al-mahmoud-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Al Shams Medical Centre</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>'+971 6 542 4255</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18237/al-shams-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Al Shams Medical Group</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Sheikh Faisal Al Qassemi Bldg, Block B, Floor 1, Suite 103, Maliha Road, Industrial Area 15, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>'+971 6 535 3581</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/342388/al-shams-medical-group</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Amritha Medical Centre</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Wahid Salim Bldg, Floor M, Flat M6, First Industrial Road, Industrial Area 5, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>'+971 6 539 7539</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/342395/amritha-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Berlin Medical Centre</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Bel Resheed Building 1, Flat 601, Al Buhairah Corniche Road, Al Majaz, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>'+971 6 544 4666</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/342396/berlin-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Central Pvt Hospital</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>'+971 6 563 9900</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153810/central-pvt-hospital</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Conceive - The Gynaecology &amp; Fertility Centre</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>'+971 6 577 1822</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18375/conceive-the-gynaecologyfertility-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Consultants Polymedic</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>P.O.Box No.692, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>'+971 6 533 5555</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/152782/consultants-polymedic</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Conceive</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>'+971 6 577 1822</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153131/conceive</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Merlin Life Sciences</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>182 Sheikh Zayed Rd - Al Wasl - Dubai, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>'+971 55 587 9093</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/368791/merlin-life-sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Minal Medical Clinic</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>'+971 6 574 9610</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18851/minal-medical-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>New Zulekha Medical Centre</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Dhaid, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>'+971 6 882 8486</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153426/new-zulekha-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Riaz Medical Center</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Al Shahba, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>'+971 6 558 3351</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18948/riaz-medical-center</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Saba Physiotherapy Center</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>'+971 6 575 0077</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18964/saba-physiotherapy-center</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Saudi German Hospital Group</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>'+971 6 556 9900</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153829/saudi-german-hospital-group</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Scottish Dental Clinic</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Crystal Plaza,Corniche Road, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>'+971 6 573 7888</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18982/scottish-dental-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Sunny's Clinic, Dr</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>'+971 6 538 8966</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153091/sunnys-clinic-dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Universal Mediators Fze</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>P.O. Box 69155, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>'+971 6 566 2416</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/148778/universal-mediators-fze</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Widex Emirates Hearing Care</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>'+971 6 574 4734</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/19059/widex-emirates-hearing-care</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Zulekha Medical Centre</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>'+971 6 553 8156</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/19073/zulekha-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Al Qassimi Hospital</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Wasit St - Mughaidir Suburb - Al Khezamia , Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>'+971 6 538 6444</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/342367/al-qassimi-hospital</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Al Qasimia Hospital</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Wasit St - Mughaidir Suburb - Al Khezamia , Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>'+971 6 538 6444</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153819/al-qasimia-hospital</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Private Rehabilitation Center</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Al Rowdat Suburb - Al Malha , Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>'+971 6 511 9000</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/342439/private-rehabilitation-center</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Dr Anwar Pasha Medical Clinic</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>111, Abu Dhabi Islamic Bank building, Opposite Sh Saud Masjid, Wasit Street, Samnan, P.O. Box: 47548, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>'+971 6 566 0008</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/333696/dr-anwar-pasha-medical-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Abubakar Clinic</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>'+971 6 562 3151</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153754/abubakar-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Afif Medical Centre</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>'+971 6 574 0091</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18038/afif-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Ahmed Bishr Medical Centre, Dr</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>'+971 6 574 2333</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/152785/ahmed-bishr-medical-centre-dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Al Amoodi Medical Center</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Corniche, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>'+971 6 556 8777</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18074/al-amoodi-medical-center</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Al Amoodi Medical Centre</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>'+971 6 556 8777</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153495/al-amoodi-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Al Buheira Lacnor Dairies Co. Ltd</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Industrial Area, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>'+971 6 533 1551</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/147633/al-buheira-lacnor-dairies-co-ltd</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Al Fatha F/stuff Trading Co</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>'+971 6 533 1894</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/148779/al-fatha-fstuff-trading-co</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Alia Clinic</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>'+971 6 561 8825</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18277/alia-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Ali Salem Hindi Clinic, Dr</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>'+971 6 574 6006</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153752/ali-salem-hindi-clinic-dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Al Khajah Medical Group</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>'+971 6 556 2200</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18146/al-khajah-medical-group</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Al Lulu Medical Centre</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>'+971 6 564 6252</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153349/al-lulu-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Al Maydan Refrigeration</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>'+971 6 543 3772</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/148774/al-maydan-refrigeration</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Al Maliha Medical Centre</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Dhaid, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>'+971 6 882 3334</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153757/al-maliha-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Al Nawa Medical Centre</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Al Khan, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>'+971 6 556 1610</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18188/al-nawa-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Al Nahdah Medical Centre</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>'+971 6 531 5152</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153376/al-nahdah-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Al Saraj Medical Centre</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>'+971 6 573 1735</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18230/al-saraj-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Al Sarraf Medical Center</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>'+971 6 553 8787</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18231/al-sarraf-medical-center</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Al Sawami Medical Clinic</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Bin Kamel Building, Al Arouba Street, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>'+971 6 561 7413</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18233/al-sawami-medical-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Al Safeer Medical Centre</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>'+971 6 543 2898</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153390/al-safeer-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Al Taif Medical Centre</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>'+971 6 555 8441</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18252/al-taif-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Al Wahda Dental Clinic</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>King Faisal Road, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>'+971 6 559 9011</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18262/al-wahda-dental-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Arla Nfpc</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>'+971 6 534 6767</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/147646/arla-nfpc</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Ashok Menon Clinic, Dr</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>'+971 6 553 0557</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153292/ashok-menon-clinic-dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Ayurvedic Herbal Health Centre</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>'+971 6 561 5434</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153508/ayurvedic-herbal-health-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Baras Al Khaimahat International</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Industrial Area 11, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>'+971 6 534 1334</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/148783/baras-al-khaimahat-international</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Basil Medical Clinic</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>'+971 6 574 6646</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18329/basil-medical-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Dallas Medical Center</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>386b Wasit Road, Al Falaj, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>'+971 6 562 7778</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/342399/dallas-medical-center</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Dental Care Centre</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Al Qassimiyah Tower,Al Mina Street, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>'+971 6 572 7515</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18401/dental-care-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Dhia H Mahdi, Dr</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>'+971 6 572 7044</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153375/dhia-h-mahdi-dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Diana Dental Clinic</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>'+971 6 562 1777</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18411/diana-dental-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Dr Ahmed Bishr Medical Centre</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>'+971 6 574 2333</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18431/dr-ahmed-bishr-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Dr Amal Al Qedrah Specialist Clinic</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Wasit Road, Al Abar, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>'+971 6 523 8883</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/342400/dr-amal-al-qedrah-specialist-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Dr Joseph Dental Clinic</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>'+971 6 555 1937</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18491/dr-joseph-dental-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Dr Mohd Tharwat Dental Clinic</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>'+971 6 563 6192</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18530/dr-mohd-tharwat-dental-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Dr Sanjay Medical Centre</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Mubarak Centre, Al Arouba Street, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>'+971 6 562 6525</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18578/dr-sanjay-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Dr Sadeq Al Sahaf</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Al Wahda St, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>'+971 6 533 8732</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18567/dr-sadeq-al-sahaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Dr Samir Ali Murad Dental Clinic</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>'+971 6 574 2434</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18576/dr-samir-ali-murad-dental-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>East Coast Clinic</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>'+971 9 238 6389</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153118/east-coast-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Enjab Medical Centre</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>'+971 6 556 3433</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153344/enjab-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Esfandyar Polyclinic</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Al Arouba Street, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>'+971 6 562 3722</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18636/esfandyar-polyclinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Fetal Medicine Clinic</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>'+971 6 577 5700</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153364/fetal-medicine-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Future Orthodontic Dental Clinic</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Al Wahda Street, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>'+971 6 553 5228</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18666/future-orthodontic-dental-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>German Medical Clinic</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>'+971 6 575 0280</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18679/german-medical-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Gopi Medical Clinic</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Industrial Area 2, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>'+971 6 542 3399</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18690/gopi-medical-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Gulf Ayurvedic Centre</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Al Arouba Street, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>'+971 6 561 6016</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18695/gulf-ayurvedic-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Gulf Medical Projects Company</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Po Box 3499, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>'+971 2 621 7715</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/239069/gulf-medical-projects-company</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Habib (dr) Ent Clinic</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>'+971 6 572 7767</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153532/habib-dr-ent-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Hakim Medical Center</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>'+971 6 559 9234</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18709/hakim-medical-center</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Jeena Clinic</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>'+971 6 562 5634</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18758/jeena-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Joseph Dental Clinic, Dr</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>'+971 6 555 1937</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153244/joseph-dental-clinic-dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Kalba Medical Center</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Kalba, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>'+971 9 277 7002</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153294/kalba-medical-center</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Khalid Polyclinic</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Al Arouba Street, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>'+971 6 561 8335</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18779/khalid-polyclinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Knan Dental Clinic</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Jamal Abdul Naser Street, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>'+971 6 559 9828</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18788/knan-dental-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Kuwait Danish Dairy Co. Kcsc, The</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Industrial Area 7, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>'+971 6 543 7388</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/147640/kuwait-danish-dairy-co-kcsc-the</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Laika Wali Medical Clinic</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>'+971 6 563 0447</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153362/laika-wali-medical-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Legend Clinic</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>'+971 6 533 3951</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153360/legend-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Mampilly Clinic</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>'+971 6 561 6464</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153527/mampilly-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Mandar Medical Clinic, Dr</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>'+971 6 568 5557</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153423/mandar-medical-clinic-dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Med Pharma</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Po Box 25235, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>'+971 6 544 0555</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/243414/med-pharma</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Metawi Medical Paediatrician Clinic</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>'+971 6 572 2999</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153332/metawi-medical-paediatrician-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Mohd A El Nounou Clinic, Dr</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>'+971 6 556 5656</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153384/mohd-a-el-nounou-clinic-dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Mohd Tharwat Dental Clinic, Dr</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>'+971 6 563 6192</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153730/mohd-tharwat-dental-clinic-dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Mouen Junblat Medical Centre, Dr</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>'+971 6 553 8238</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153506/mouen-junblat-medical-centre-dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>National Agric Dev Co, The</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>P.O Box 26909, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>'+971 6 573 6500</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/147666/national-agric-dev-co-the</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Nathani Clinic</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>'+971 6 562 3834</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153394/nathani-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>National Center for Modern Medicine</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Wasit Road, Al Falaj, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>'+971 6 523 3300</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/342435/national-center-for-modern-medicine</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Noor Clinic</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Al Arooba Road, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>'+971 6 568 4974</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18905/noor-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Our Own Medical and Diagnostics Center</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>'+971 6 573 7735</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18911/our-own-medical-and-diagnostics-center</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Our Own Medical &amp; Diagnostics Center</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>'+971 6 573 7735</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153243/our-own-medicaldiagnostics-center</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>PHARMACARE LIMITED</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>SAIF Zone (Unit C), P.O. Box: 8336, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>'+971 6 557 1797</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/246461/pharmacare-limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Private Eye Clinic</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Al Arouba Street, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>'+971 6 562 5890</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18928/private-eye-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Psychiatric Clinic</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>'+971 6 573 7789</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153370/psychiatric-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Raad Al Qasik Medical Centre, Dr</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>'+971 6 574 4677</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153366/raad-al-qasik-medical-centre-dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Rania Al Qedrah Specialized Clinic, Dr</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>'+971 6 572 2330</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153348/rania-al-qedrah-specialized-clinic-dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Reem Medical Diagnostic Centre</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>'+971 6 562 0831</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153379/reem-medical-diagnostic-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Reem Specialists Medical Center</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>'+971 6 562 5422</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153729/reem-specialists-medical-center</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Rishil Poly Clinic</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Al Arouba Street, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>'+971 6 561 2900</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18950/rishil-poly-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Sadeq Al Sahaf, Dr</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>'+971 6 533 8732</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153324/sadeq-al-sahaf-dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Sajida Medical Centre</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Al Wasit Street, Samnan Area, P.O. Box: 31278, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>'+971 6 567 6027</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18969/sajida-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Samir Abu Zied Clinic, Dr</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>104, Galilee building, Jamal Abdul Nasr St, P.O. Box: 22741, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>'+971 6 553 7007</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153248/samir-abu-zied-clinic-dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Samia Khedr Medical Clinic, Dr</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>'+971 6 556 5589</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153357/samia-khedr-medical-clinic-dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Samir Ali Murad Dental Clinic, Dr</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>'+971 6 574 2434</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153760/samir-ali-murad-dental-clinic-dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Sanjay Medical Centre, Dr</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>'+971 6 562 6525</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153257/sanjay-medical-centre-dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Sarhad Medical Clinic</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>'+971 6 568 2670</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18977/sarhad-medical-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Sasil's Dental Clinic</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>'+971 6 562 6957</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18978/sasils-dental-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Shakir S Vali, Dr</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>'+971 6 563 6308</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153824/shakir-s-vali-dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Solanki Dental Centre</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>'+971 6 561 6556</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153335/solanki-dental-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Suha Al-Farhan Children Dentist, Dr</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>'+971 6 573 7242</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153356/suha-al-farhan-children-dentist-dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Swedish Clinic</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>'+971 6 573 0666</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/19012/swedish-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>United Dairies</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>'+971 6 533 9196</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/147639/united-dairies</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Venniyil Clinic</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>P.O Box 1100, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>'+971 6 568 2258</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153114/venniyil-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Wassim Kabbani Clinic, Dr</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>'+971 6 572 1313</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153351/wassim-kabbani-clinic-dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Wilson Specialized Hospital</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>'+971 6 577 1757</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr"/>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153820/wilson-specialized-hospital</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>W Wilson Health Care Group</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>'+971 6 577 1757</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/19052/w-wilson-health-care-group</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Al Maliky Dental Clinic</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>'+971 6 538 8205</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18159/al-maliky-dental-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>AL Riyadh Medical Equipments Centre</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Po Box 3805, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr"/>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/226714/al-riyadh-medical-equipments-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Al Shrook Polyclinic</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Al Arouba Street, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>'+971 6 568 5022</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18246/al-shrook-polyclinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>AL Taheal Medical Equipment</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Po Box 515, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/228491/al-taheal-medical-equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Ambegaokar Clinic</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>'+971 6 568 7728</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr"/>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18284/ambegaokar-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Delta Medical Clinic</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>'+971 6 562 0404</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr"/>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18397/delta-medical-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Dr Labib Al Hasan Medical Clinic</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>King Abdul Aziz Road, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>'+971 6 573 6466</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18501/dr-labib-al-hasan-medical-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Hyma Medical Clinic</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>'+971 6 561 5754</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr"/>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18730/hyma-medical-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Hyma Medical Clinic (hemalatha, Dr)</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>'+971 6 561 5754</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr"/>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153325/hyma-medical-clinic-hemalatha-dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>IBN RUSHD MEDICAL DRUGS EQUIPMENT STORE</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Po Box 21271, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr"/>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/240124/ibn-rushd-medical-drugs-equipment-store</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Labib Al Hasan Medical Clinic, Dr</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>'+971 6 573 6466</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr"/>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153434/labib-al-hasan-medical-clinic-dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Mediplus Diagnostic Centre</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Mubarak Centre, Office 303,Al Arouba Street, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>'+971 6 563 4347</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr"/>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18839/mediplus-diagnostic-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Zafar Dental Clinic</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Kalba, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>'+971 9 277 7351</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr"/>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153411/zafar-dental-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Al Dallah Medical Clinic</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Al Arouba Street, Umm Tarrafa, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>'+971 6 561 4266</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr"/>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18091/al-dallah-medical-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Al Jawhara Medical Center</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Al Bana Building, Jamal Abdul Nasser Street,Al Majaz 2, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>'+971 6 555 1231</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr"/>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18136/al-jawhara-medical-center</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Al Lulu Medical Center</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>'+971 6 564 6252</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr"/>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18150/al-lulu-medical-center</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Al Mushtaq Medical Centre</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Baghlaf Building,Al Arooba Street, Al Marijah, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>'+971 6 568 6511</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr"/>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18179/al-mushtaq-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Al Qassemi Hospital</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Wasit Street, Al Khezammia, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>'+971 6 538 6444</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr"/>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/17633/al-qassemi-hospital</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Al Rai Medical Centre</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Al Kabayel Building, Floor 1, Office 14,Al Hisn Avenue, Al Marijah, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>'+971 6 568 7893</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr"/>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18209/al-rai-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Al Zahra Pvt Hospital</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>'+971 6 561 9999</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153809/al-zahra-pvt-hospital</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Bhatia Clinic</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Al Arouba Street, Al Shuwaiheen, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>'+971 6 568 1717</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr"/>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18333/bhatia-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Dabbous Medical Centre</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Al Arouba Street, Al Naba'ah, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>'+971 6 563 6552</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr"/>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18387/dabbous-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Davis Dental Clinic</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>301, Corniche Plaza 1, Al Buhairah, P.O. Box: 1092, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>'+971 6 572 5626</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18392/davis-dental-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Dr Mouen Junblat Dental Clinic</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Jamal Abdul Nasser St, Al Majaz 2, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>'+971 6 553 8238</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr"/>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18532/dr-mouen-junblat-dental-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Dr Oras Sharif Clinic</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Al Wahda Street, Bu Danig, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>'+971 6 574 1313</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr"/>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18550/dr-oras-sharif-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Dr Said H Muwafi</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Corniche Plaza 2, Corniche Street,Al Majaz 1, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>'+971 6 572 1919</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr"/>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18570/dr-said-h-muwafi</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Dr Saleh Mohammed Saleh</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Corniche Plaza 2, Corniche Street,Al Majaz 1, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>'+971 6 572 2458</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr"/>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18572/dr-saleh-mohammed-saleh</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>DYNAMIC REHAB MEDICAL CENTRE</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Po Box 48556, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr"/>
+      <c r="D276" t="inlineStr"/>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/236155/dynamic-rehab-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Family Clinic</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Al Majaz Tower, Jamal Abdul Nasser Street,Al Majaz 2, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>'+971 6 555 2150</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr"/>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18650/family-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Jessy Clinic</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Al Arouba Street, Al Ghuwair, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>'+971 6 561 8300</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr"/>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18763/jessy-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Lyla Dental Clinic</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Al Arouba Street, Al Ghuwair, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>'+971 6 561 5307</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18798/lyla-dental-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Rolla Clinic</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Al Arouba Street, Al Marijah, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>'+971 6 568 3405</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr"/>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18951/rolla-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Romira Paediatric Clinic</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Al Zahraa Street, Al Naba'ah, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>'+971 6 563 5201</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18952/romira-paediatric-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Specialized Medical Center</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Corniche Street, Al Majaz 1, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>'+971 6 573 6800</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr"/>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/19006/specialized-medical-center</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Dr Gill's Clinic</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Lagoon Towers, Corniche Street,Al Majaz 1, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>'+971 6 572 4484</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr"/>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18468/dr-gills-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>AL Ameen Medical Centre</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Po Box 1837, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr"/>
+      <c r="D284" t="inlineStr"/>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/218254/al-ameen-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Assi Dental Clinic, Dr</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>'+971 6 555 1981</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr"/>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/152776/assi-dental-clinic-dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>New Al Qassemiya Hospital</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>'+971 6 538 6444</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr"/>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153808/new-al-qassemiya-hospital</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Modern Clinic</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Modern Clinic Building, King Faizal Road, Abu Shagara, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>'+971 6 542 0066</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr"/>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/364526/modern-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Abdulla Semrin Clinic, Dr</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>'+971 6 573 3440</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr"/>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153339/abdulla-semrin-clinic-dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Adnan Ballout Clinic, Dr</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>'+971 6 555 1231</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr"/>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153504/adnan-ballout-clinic-dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Advanced Eye Clinic</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>'+971 6 556 1220</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr"/>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18036/advanced-eye-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Al Ahlia Regional Medical Centre</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Ibrahim Mohd Al Midfa Street, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>'+971 6 562 1700</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr"/>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18059/al-ahlia-regional-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Al Amanah Medical Centre</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Al Mubarak Centre, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>'+971 6 561 5545</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr"/>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18071/al-amanah-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Al Ansari Clinic</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>'+971 6 561 6828</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr"/>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/152760/al-ansari-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>AL ARAIMI GEN TRADING LLC</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>'+971 6 534 8384</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr"/>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/302790/al-araimi-gen-trading-llc</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Al Alfiah Dental Clinic</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>506, Al Majaz Pearl Tower, Opposite Al Majaz Park, Al Majaz, P.O. Box: 24856, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>'+971 6 555 9905</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr"/>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/333726/al-alfiah-dental-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Al Barakah Medical Clinic</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>'+971 6 543 1763</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr"/>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18085/al-barakah-medical-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Al Baras Al Khaimahah Medical Clinic</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>'+971 6 543 1763</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/152771/al-baras-al-khaimahah-medical-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Al Batool Complex Medical</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>'+971 6 572 7175</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr"/>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153105/al-batool-complex-medical</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Al Darary Medical Centre</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>'+971 6 533 6176</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18095/al-darary-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Al Diyafah Medical Centre</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>'+971 6 532 0800</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr"/>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153731/al-diyafah-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Al Fanar Food Industries LLC</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Industrial Area 11, Str No 20, P.O. Box: 20857, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>'+971 6 534 3870</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr"/>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/331951/al-fanar-food-industries-llc</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Al Huda Polyclinic</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>'+971 6 556 2444</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/152778/al-huda-polyclinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Al Ishraf Medical Centre</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Al Arouba Street, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>'+971 6 561 3613</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr"/>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18128/al-ishraf-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Al Ishraf Medical Center</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>'+971 6 561 3613</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr"/>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153305/al-ishraf-medical-center</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Al Majaz Medical Centre</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>'+971 6 556 5660</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr"/>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18156/al-majaz-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Al Muntasir Medical Centre</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Buhaira Centre, Suite 204, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>'+971 6 573 9545</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr"/>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18176/al-muntasir-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Al Maliky Dental Clinic</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Al Wasit Road, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>'+971 6 538 8205</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr"/>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18160/al-maliky-dental-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>AL MUFID TRADING COMPANY L.L.C.</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>678, Natl Rent A Car building, Next to Oasis Centre, Sh Zayed Road, P.O. Box: 4636, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>'+971 4 338 3339</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr"/>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/224696/al-mufid-trading-company-llc</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Al Nakheel Medical Centre</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Rolla Mall, Al Arouba Street, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>'+971 6 561 8899</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr"/>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18185/al-nakheel-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Al Naeem Medical Center</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>'+971 6 561 2696</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr"/>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18181/al-naeem-medical-center</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Al Raha Medical Center</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>'+971 6 533 4415</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18204/al-raha-medical-center</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Al Rubiyan Trading Company LLC</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Behind Igloo Ice-cream, Industrial Area 2, P.O. Box: 37966, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>'+971 6 533 3913</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr"/>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/318786/al-rubiyan-trading-company-llc</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Al-Rimal Foodstuff Inds FZC</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>L2-03, SAIF Zone, P.O. Box: 7889, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>'+971 6 557 5075</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr"/>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/332063/al-rimal-foodstuff-inds-fzc</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Al Saadah Medical Center</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>'+971 6 562 3949</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18218/al-saadah-medical-center</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Al Safa Clinic</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>106, Al Fardan building, Clock Tower Round About, P.O. Box: 19515, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>'+971 6 563 5211</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr"/>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18219/al-safa-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Al Saha Wa Al Shifaa Specialities Complex</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Rolla Mall, Al Arouba Street, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>'+971 6 563 2618</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr"/>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18223/al-saha-wa-al-shifaa-specialities-complex</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Al Shams Food Industries</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>'+971 6 532 5327</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/148788/al-shams-food-industries</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>AL SHULLA VET CENTER</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>P.O. Box: 20296, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>'+971(6)379735</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/299592/al-shulla-vet-center</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Al Soha and Al Shifa Specialities Complex</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>307, Rolla Mall, Rolla, P.O. Box: 62880, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>'+971 6 563 2618</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr"/>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/333639/al-soha-and-al-shifa-specialities-complex</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Al Thequah Clinic</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>'+971 6 572 7757</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr"/>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153338/al-thequah-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Al Wafir Medical Centre</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Near Natl Paints Round About, Industrial Area 11, P.O. Box: 97433, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>'+971 6 534 7494</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr"/>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18259/al-wafir-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Al Widad Specialist Clinic</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Corniche Plaza, Office 301, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>'+971 6 574 9666</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr"/>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18266/al-widad-specialist-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Al Widad Specialist</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>301, Corniche Plaza II, P.O. Box: 61718, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>'+971 6 574 9666</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr"/>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/333683/al-widad-specialist</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>AL ZAHAR HOSPITAL</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>P.O. Box: 3499, SHARJAH , UAE</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>'+971 6 561 9999</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr"/>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/299495/al-zahar-hospital</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Amal Abdel Kader Dental Clinic</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>803, Al Durrah Tower, Buhairah Corniche, P.O. Box: 8720, Dubai, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>'+971 6 556 5564</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr"/>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18282/amal-abdel-kader-dental-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Anthony Medical Centre</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>'+971 6 563 0555</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr"/>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18299/anthony-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Antony Medical Centre</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>'+971 6 563 0555</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr"/>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/152770/antony-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Apollo Medical Clinic</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>'+971 6 538 7199</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr"/>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18301/apollo-medical-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>BANIYAS MEDICAL EQUIPMENT TRADING</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>King Faisal St, P.O. Box: 31418, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>'+971 6 574 8290</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr"/>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/232623/baniyas-medical-equipment-trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Bilal Medical Centre</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Next to Dynatrade, Caterpillar Road, P.O. Box: 41347, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>'+971 6 532 8558</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr"/>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/333644/bilal-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Chithra Shamsudheen's Clinic, Dr</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>'+971 6 562 0181</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr"/>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153272/chithra-shamsudheens-clinic-dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Chinese Clinic, The</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>'+971 6 568 5466</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr"/>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153734/chinese-clinic-the</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Cocoon - Individualized Natal Care</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>'+971 6 524 3444</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr"/>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18372/cocoon-individualized-natal-care</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Consultant Polymedic</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Darwesh Building, Al Wahda Street, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>'+971 6 533 5555</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr"/>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18376/consultant-polymedic</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Derma Health</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Musallah, P.O. Box: 40096, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>'+971 6 561 8801</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr"/>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/333736/derma-health</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Deva Medical Centre</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>'+971 6 558 4335</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr"/>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18408/deva-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Dr Chithra Shamsudheen's Clinic</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Al Ghurair Tower, Apt 303,Al Arouba Street, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>'+971 6 562 0181</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr"/>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18453/dr-chithra-shamsudheens-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Dr Maged Salah Eldin</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>'+971 6 561 6261</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18506/dr-maged-salah-eldin</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Dr Mariyam Dental Clinic</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>'+971 6 573 9899</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr"/>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18515/dr-mariyam-dental-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Dr Mohd Ahmed Ali Dental Clinic</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Sharjah , United Arab Emirates, UAE</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>'+971 6 555 2116</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr"/>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18525/dr-mohd-ahmed-ali-dental-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Dr Rabha Habib El Sayegh Clinic</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Al Durra Tower, Office 806,Corniche Road, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>'+971 6 556 5568</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18551/dr-rabha-habib-el-sayegh-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Dr Ravindran Gopal Clinic</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Al Arouba Street, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>'+971 6 569 0569</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr"/>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/18558/dr-ravindran-gopal-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Emirates Pvt Poly Clinic</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>'+971 6 555 1666</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/152775/emirates-pvt-poly-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>EMIRATES MEDICAL LAB</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Po Box 26826, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>'+971 6 573 6866</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr"/>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/236644/emirates-medical-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Enjab Hospital for Day Care</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Al Durrah Tower, Corniche Al Buhairah, P.O. Box: 31705, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>'+971 6 556 3433</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr"/>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/333741/enjab-hospital-for-day-care</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Ent Specialized Clinic</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>704, Al Durra Tower, Buheira Corniche, P.O. Box: 26150, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>'+971 6 556 0002</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr"/>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153409/ent-specialized-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Gayatree Medical Centre</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>'+971 6 559 1110</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr"/>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153112/gayatree-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Hayat Medical Centre</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>'+971 6 568 5620</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr"/>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153117/hayat-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Hejazi's Clinic, Dr</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>'+971 6 563 5029</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr"/>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153308/hejazis-clinic-dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Islamic Medical Herbs Treatment Center</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>'+971 6 568 7000</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr"/>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153438/islamic-medical-herbs-treatment-center</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>ISMAIL MOHD AL NIMIR</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Po Box 24044, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>'+971 6 568 7255</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr"/>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/240841/ismail-mohd-al-nimir</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Jwan S Murad Clinic, Dr</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>'+971 6 572 4855</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr"/>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153361/jwan-s-murad-clinic-dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Kottakkal Health Massage</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>'+971 6 562 4725</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr"/>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153249/kottakkal-health-massage</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Maged Salah El Din Clinic, Dr</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>'+971 6 561 6261</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153746/maged-salah-el-din-clinic-dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Malek A Nawas, Dr</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>'+971 6 572 6272</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153371/malek-a-nawas-dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Malek Abdulla Nawas, Dr</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Corniche, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>'+971 6 572 6272</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153387/malek-abdulla-nawas-dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Mandar Medical Centre</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>32, Natl Bank of Abu Dhabi Building, Bank Street, Rolla, P.O. Box: 2722, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>'+971 6 568 5557</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr"/>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/333664/mandar-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Mariyam Dental Clinic, Dr</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>'+971 6 573 9899</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr"/>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153262/mariyam-dental-clinic-dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Metawi Medical Clinic</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>'+971 6 572 2999</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr"/>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153381/metawi-medical-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Minal Specialised Clinic Dermatology</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>401, C Block, Crystal Plaza, Buhaira Corniche, P.O. Box: 24680, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>'+971 6 574 9610</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr"/>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/333734/minal-specialised-clinic-dermatology</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Mohd Ahamad Ali Dental Clinic, Dr</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>'+971 6 555 2116</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr"/>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153510/mohd-ahamad-ali-dental-clinic-dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Mount Seena Medical Centre</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Al Arouba Street, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>'+971 6 561 7755</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr"/>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/153331/mount-seena-medical-centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>NADD AL SHIBA VET CLINIC</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>P.O. Box: 53694, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>'+971(6)384166</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr"/>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/299599/nadd-al-shiba-vet-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Nanda Medical Centre</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Mashreqbank building, Natl Paints Round About, Industrial Area 11, P.O. Box: 19585, Sharjah , UAE</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>'+971 6 534 6522</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr"/>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>https://www.yello.ae/company/333669/nanda-medical-centre</t>
         </is>
       </c>
     </row>

--- a/yello_doctor_sharjah.xlsx
+++ b/yello_doctor_sharjah.xlsx
@@ -459,7 +459,11 @@
           <t>'+971 6 565 0690</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/344092/al-abqari-dental-clinic</t>
@@ -482,7 +486,11 @@
           <t>'+971 6 561 7822</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>info@vedhansh.com</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/351899/austin-center-for-rehabilitation-of-person-with-disabilities</t>
@@ -505,7 +513,11 @@
           <t>'+971 6 566 7996</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/354307/sunny-sharqan-medical-centre</t>
@@ -528,7 +540,11 @@
           <t>'+971 6 559 0007</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/352212/al-afdal-medical-center</t>
@@ -551,7 +567,11 @@
           <t>'+971 6 525 3756</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/356351/mulk-physiotherapy-center</t>
@@ -574,7 +594,11 @@
           <t>'+971 6 550 3558</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/343954/ibtisamty-dental-clinic</t>
@@ -597,7 +621,11 @@
           <t>'+971 6 521 8889</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/374124/shifa-al-jazeera-medical-centre-llc</t>
@@ -620,7 +648,11 @@
           <t>'+971 6 506 0000</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/17710/zulekha-hospital</t>
@@ -643,7 +675,11 @@
           <t>'+971 6 566 7661</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>alamumahmc@gmail.com</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/352120/dr-uma-maheswari</t>
@@ -666,7 +702,11 @@
           <t>'+971 6 559 1985</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/349515/al-elaj-medical-equipment-tr</t>
@@ -689,7 +729,11 @@
           <t>'+971 6 526 6885</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/347642/art-medical-center</t>
@@ -712,7 +756,11 @@
           <t>'+971 6 568 8600</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/358083/asala-medical-center</t>
@@ -735,7 +783,11 @@
           <t>'+971 6 567 1707</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/347083/al-bawadi-medicaldiagnostic-center</t>
@@ -758,7 +810,11 @@
           <t>'+971 6 555 1575</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/355131/right-medical-centre</t>
@@ -781,7 +837,11 @@
           <t>'+971 6 561 2737</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18028/abrahams-medical-centre</t>
@@ -804,7 +864,11 @@
           <t>'+971 6 530 6161</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/362487/ahlan-medical-center</t>
@@ -827,7 +891,11 @@
           <t>'+971 6 553 0557</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18451/dr-ashok-menon-clinic</t>
@@ -850,7 +918,11 @@
           <t>'+971 6 574 4529</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18042/ahalia-medical-centre</t>
@@ -873,7 +945,11 @@
           <t>'+971 6 535 3582</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/342387/al-shams-medicaldiagnostic-centre</t>
@@ -896,7 +972,11 @@
           <t>'+971 6 557 1132</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/207709/bentham-science-publishers-ltd-fzc</t>
@@ -919,7 +999,11 @@
           <t>'+971 6 573 7005</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>info@bissanmc.com</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153264/bissam-medical-centre</t>
@@ -942,7 +1026,11 @@
           <t>'+971 6 522 4422</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/359495/california-dental-clinic</t>
@@ -965,7 +1053,11 @@
           <t>'+971 6 565 2332</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18370/class-medical-centre</t>
@@ -988,7 +1080,11 @@
           <t>'+971 6 575 2200</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18924/prime-medical-center-sharjah</t>
@@ -1011,7 +1107,11 @@
           <t>'+971 6 562 5234</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153395/yathish-kamath-dr-mds-marina-medical-centre</t>
@@ -1034,7 +1134,11 @@
           <t>'+971 6 562 3151</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18032/abubakr-clinic</t>
@@ -1057,7 +1161,11 @@
           <t>'+971 50 424 9032</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/367437/adam-veterinary-medicines-llc</t>
@@ -1080,7 +1188,11 @@
           <t>'+971 6 556 2200</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/222958/al-khaja-medical-clinic</t>
@@ -1103,7 +1215,11 @@
           <t>'+971 6 563 2618</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/361038/al-saha-al-shifa</t>
@@ -1126,7 +1242,11 @@
           <t>'+971 6 575 3888</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/17647/bhatia-medical-centre</t>
@@ -1149,7 +1269,11 @@
           <t>'+971 6 563 2100</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18416/doctors-medical-centre</t>
@@ -1172,7 +1296,11 @@
           <t>'+971 52 277 5005</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/364544/dr-zains-homeopathic-clinic-sharjah</t>
@@ -1195,7 +1323,11 @@
           <t>'+971 6 530 9898</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/367702/elite-medical-center</t>
@@ -1218,7 +1350,11 @@
           <t>'+971 6 518 0800</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/362215/ishaq-bin-omran-medical-center-ibo</t>
@@ -1241,7 +1377,11 @@
           <t>'+971 6 525 1000</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/347798/oriana-hospital</t>
@@ -1264,7 +1404,11 @@
           <t>'+971 6 568 2258</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/25748/venniyil-medical-centre</t>
@@ -1287,7 +1431,11 @@
           <t>'+971 6 534 4439</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18143/al-kanary-medical-clinic</t>
@@ -1310,7 +1458,11 @@
           <t>'+971 6 505 7048</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/341538/university-hospital-sharjah</t>
@@ -1333,7 +1485,11 @@
           <t>'+971 600520057</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/371303/hygiene-fresh</t>
@@ -1356,7 +1512,11 @@
           <t>'+971 6 566 7661</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/352098/al-amumah-medical-center</t>
@@ -1379,7 +1539,11 @@
           <t>'+971 6 530 4900</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/353173/lifeway-specialized-medical-centre</t>
@@ -1402,7 +1566,11 @@
           <t>'+971 6 566 8745</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18875/nahar-mampilly-medical-centre</t>
@@ -1425,7 +1593,11 @@
           <t>'+971 6 533 7864</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/148789/unipex-dairy-products-co-ltd</t>
@@ -1448,7 +1620,11 @@
           <t>'+971 6 556 9888</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/350245/al-durrah-radiology-center</t>
@@ -1471,7 +1647,11 @@
           <t>'+971 6 569 1791</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/19188/al-watania-veterinary-clinic</t>
@@ -1494,7 +1674,11 @@
           <t>'+971 6 882 2270</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/349667/al-ysra-medical-center</t>
@@ -1517,7 +1701,11 @@
           <t>'+971 6 524 5444</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18380/cosme-surge</t>
@@ -1540,7 +1728,11 @@
           <t>'+971 50 860 6857</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/19201/europets-hospital</t>
@@ -1563,7 +1755,11 @@
           <t>'+971 6 534 3803</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/319890/grade-refrigeration-llc</t>
@@ -1586,7 +1782,11 @@
           <t>'+971 6 509 5555</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/371813/gulf-medical-projects</t>
@@ -1609,7 +1809,11 @@
           <t>'+971 6 518 0800</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/360000/ibo</t>
@@ -1632,7 +1836,11 @@
           <t>'+971 6 530 4900</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/366850/lifeway-specialized-medical-centre</t>
@@ -1655,7 +1863,11 @@
           <t>'+971 50 963 8577</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/361312/best-gynaecologist-in-uae</t>
@@ -1678,7 +1890,11 @@
           <t>'+971 6 573 8088</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/333177/international-radiology-centre</t>
@@ -1701,7 +1917,11 @@
           <t>'+971 6 525 4446</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/362584/new-hope-ivf</t>
@@ -1724,7 +1944,11 @@
           <t>'+971 6 561 5545</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18070/al-amanah-medical-centre</t>
@@ -1747,7 +1971,11 @@
           <t>'+971 6 561 7277</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18155/al-mahmood-medical-centre</t>
@@ -1770,7 +1998,11 @@
           <t>'+971 6 561 4262</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18224/al-salam-clinic</t>
@@ -1793,7 +2025,11 @@
           <t>'+971 50 252 5966</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/373035/al-sherouq-medical-center</t>
@@ -1816,7 +2052,11 @@
           <t>'+971 6 556 3969</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/373835/al-safwa-radiology-center</t>
@@ -1839,7 +2079,11 @@
           <t>'+971 6 563 6308</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/17650/central-private-hospital</t>
@@ -1862,7 +2106,11 @@
           <t>'+971 56 563 6802</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/357446/desert-mart</t>
@@ -1885,7 +2133,11 @@
           <t>'+971 6 555 1666</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18635/emirates-private-poly-clinic</t>
@@ -1908,7 +2160,11 @@
           <t>'+971 6 572 5551</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/365301/eve-fertility-center</t>
@@ -1931,7 +2187,11 @@
           <t>'+971 6 574 4266</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18661/french-rheumatism-clinic</t>
@@ -1954,7 +2214,11 @@
           <t>'+971 50 963 8577</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/363115/gynaecologist-in-sharjah</t>
@@ -1977,7 +2241,11 @@
           <t>'+971 6 539 4466</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/241300/julphar-drug-store-sharjah</t>
@@ -2000,7 +2268,11 @@
           <t>'+971 6 565 2929</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/360495/medical-center-in-sharjah</t>
@@ -2023,7 +2295,11 @@
           <t>'+971 6 574 9610</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18850/minal-medical-clinic</t>
@@ -2046,7 +2322,11 @@
           <t>'+971 6 568 6200</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18880/nathani-medical-centre</t>
@@ -2069,7 +2349,11 @@
           <t>'+971 6 553 6936</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18896/new-medical-centre</t>
@@ -2092,7 +2376,11 @@
           <t>'+971 6 562 5422</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18943/reem-specialists-medical-centre</t>
@@ -2115,7 +2403,11 @@
           <t>'+971 6 558 1515</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/17691/royal-hospital</t>
@@ -2138,7 +2430,11 @@
           <t>'+971 6 575 1222</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/17696/sharjah-corniche-hospital</t>
@@ -2161,7 +2457,11 @@
           <t>'+971 6 561 6556</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/19000/solanki-dental-center</t>
@@ -2184,7 +2484,11 @@
           <t>'+971 6 530 5882</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18047/ahlan-dental-clinic</t>
@@ -2207,7 +2511,11 @@
           <t>'+971 6 555 1981</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18555/dr-ramzi-assi-dental-clinic</t>
@@ -2230,7 +2538,11 @@
           <t>'+971 6 557 0722</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/147645/al-ain-farms-for-livestock-production</t>
@@ -2253,7 +2565,11 @@
           <t>'+971 6 561 3030</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/348714/optimum-medical-center</t>
@@ -2276,7 +2592,11 @@
           <t>'+971 4 323 1889</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/371138/dermahealth</t>
@@ -2295,7 +2615,11 @@
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18770/jwan-murad-fertility-clinic</t>
@@ -2318,7 +2642,11 @@
           <t>'+971 6 556 2727</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/152772/abdul-ghani-siddique-ent-clinic-dr</t>
@@ -2341,7 +2669,11 @@
           <t>'+971 6 562 1700</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18057/al-ahalia-regional-medical-centre</t>
@@ -2364,7 +2696,11 @@
           <t>'+971 6 559 9699</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18089/al-buhairah-medical-centre</t>
@@ -2387,7 +2723,11 @@
           <t>'+971 6 559 9147</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/19179/al-faseel-veterinarypet-clinic</t>
@@ -2410,7 +2750,11 @@
           <t>'+971 6 562 4456</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18130/al-jahharah-dental-clinic</t>
@@ -2433,7 +2777,11 @@
           <t>'+971 6 561 7577</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18280/alpha-medical-centre</t>
@@ -2456,7 +2804,11 @@
           <t>'+971 6 538 9999</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/228848/al-thiqah-club-for-handicapped</t>
@@ -2479,7 +2831,11 @@
           <t>'+971 6 559 4454</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18296/annie-dental-clinic</t>
@@ -2502,7 +2858,11 @@
           <t>'+971 6 557 3559</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/147655/aqsa-international-fzc</t>
@@ -2525,7 +2885,11 @@
           <t>'+971 6 530 3999</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/361501/best-physiotherapy-clinic-in-sharjah</t>
@@ -2548,7 +2912,11 @@
           <t>'+971 6 559 2930</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18388/dablan-dental-clinic</t>
@@ -2571,7 +2939,11 @@
           <t>'+971 6 574 6006</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18437/dr-ali-salem-hindi-clinic</t>
@@ -2594,7 +2966,11 @@
           <t>'+971 6 572 7700</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18449/dr-asad-i-dajani-specialized-centre</t>
@@ -2617,7 +2993,11 @@
           <t>'+971 6 559 1110</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18464/dr-gayatree-medical-centre</t>
@@ -2640,7 +3020,11 @@
           <t>'+971 6 572 7767</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18469/dr-habib-ear-nosethroat-clinic</t>
@@ -2663,7 +3047,11 @@
           <t>'+971 6 563 5029</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18475/dr-hijazis-clinic</t>
@@ -2686,7 +3074,11 @@
           <t>'+971 6 568 5557</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18513/dr-mandar-medical-clinic</t>
@@ -2709,7 +3101,11 @@
           <t>'+971 6 572 1052</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18546/dr-nemat-mossalami</t>
@@ -2732,7 +3128,11 @@
           <t>'+971 6 553 7007</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18575/dr-samir-abou-zeid-clinic</t>
@@ -2755,7 +3155,11 @@
           <t>'+971 6 573 7242</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18590/dr-suha-al-farhan-clinic</t>
@@ -2778,7 +3182,11 @@
           <t>'+971 6 563 9966</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18592/dr-sunny-medical-centre</t>
@@ -2801,7 +3209,11 @@
           <t>'+971 6 562 3844</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18740/ideal-medical-centre</t>
@@ -2824,7 +3236,11 @@
           <t>'+971 6 559 5285</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18746/indulekha-medical-clinic</t>
@@ -2847,7 +3263,11 @@
           <t>'+971 6 524 2688</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18762/jennifer-skin-care-centre</t>
@@ -2870,7 +3290,11 @@
           <t>'+971 6 561 6464</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18810/mampilly-eye-clinic</t>
@@ -2893,7 +3317,11 @@
           <t>'+971 6 569 1400</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18817/marijeh-clinic</t>
@@ -2916,7 +3344,11 @@
           <t>'+971 6 562 5234</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18819/marina-medical-centre</t>
@@ -2939,7 +3371,11 @@
           <t>'+971 6 563 7719</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18831/medical-house-for-diagnosistreatment</t>
@@ -2962,7 +3398,11 @@
           <t>'+971 6 562 6922</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18836/medicare-clinic</t>
@@ -2985,7 +3425,11 @@
           <t>'+971 6 539 6200</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18841/mega-medical-centre</t>
@@ -3008,7 +3452,11 @@
           <t>'+971 6 533 9799</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18855/modern-dental-clinic</t>
@@ -3031,7 +3479,11 @@
           <t>'+971 6 561 5111</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18954/roy-dental-clinic</t>
@@ -3054,7 +3506,11 @@
           <t>'+971 6 555 3355</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18962/russian-medicalscientific-complex</t>
@@ -3077,7 +3533,11 @@
           <t>'+971 6 556 8888</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18976/sara-medical-centre</t>
@@ -3100,7 +3560,11 @@
           <t>'+971 6 553 1080</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18986/shamma-dental-clinic</t>
@@ -3123,7 +3587,11 @@
           <t>'+971 6 530 5252</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/342444/sunny-al-nahda-medical-centre</t>
@@ -3146,7 +3614,11 @@
           <t>'+971 55 390 8860</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/342445/sunny-speciality-medical-center</t>
@@ -3169,7 +3641,11 @@
           <t>'+971 6 568 2258</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/19049/venniyil-medical-centre</t>
@@ -3192,7 +3668,11 @@
           <t>'+971 6 533 3949</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/19070/ziad-e-baghdan-clinic</t>
@@ -3215,7 +3695,11 @@
           <t>'+971 6 530 3999</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/363079/cure-medical-center-physiotherapy</t>
@@ -3238,7 +3722,11 @@
           <t>'+971 6 524 2111</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/17673/kuwaiti-hospital</t>
@@ -3261,7 +3749,11 @@
           <t>'+971 55 551 2478</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/369118/yalla-doc</t>
@@ -3284,7 +3776,11 @@
           <t>'+971 6 563 1429</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18173/al-mueed-clinic</t>
@@ -3307,7 +3803,11 @@
           <t>'+971 6 561 9999</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/17640/al-zahra-private-hospital</t>
@@ -3326,7 +3826,11 @@
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/317241/cpr-select</t>
@@ -3345,7 +3849,11 @@
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/368316/niyana</t>
@@ -3368,7 +3876,11 @@
           <t>'+971 6 561 2737</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153514/abrahams-medical-clinic</t>
@@ -3391,7 +3903,11 @@
           <t>'+971 6 886 1202</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/342379/al-faiez-medical-clinic</t>
@@ -3414,7 +3930,11 @@
           <t>'+971 6 561 7277</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/152788/al-mahmoud-medical-centre</t>
@@ -3437,7 +3957,11 @@
           <t>'+971 6 542 4255</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18237/al-shams-medical-centre</t>
@@ -3460,7 +3984,11 @@
           <t>'+971 6 535 3581</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/342388/al-shams-medical-group</t>
@@ -3483,7 +4011,11 @@
           <t>'+971 6 539 7539</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/342395/amritha-medical-centre</t>
@@ -3506,7 +4038,11 @@
           <t>'+971 6 544 4666</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/342396/berlin-medical-centre</t>
@@ -3529,7 +4065,11 @@
           <t>'+971 6 563 9900</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153810/central-pvt-hospital</t>
@@ -3552,7 +4092,11 @@
           <t>'+971 6 577 1822</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18375/conceive-the-gynaecologyfertility-centre</t>
@@ -3575,7 +4119,11 @@
           <t>'+971 6 533 5555</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/152782/consultants-polymedic</t>
@@ -3598,7 +4146,11 @@
           <t>'+971 6 577 1822</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153131/conceive</t>
@@ -3621,7 +4173,11 @@
           <t>'+971 55 587 9093</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/368791/merlin-life-sciences</t>
@@ -3644,7 +4200,11 @@
           <t>'+971 6 574 9610</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18851/minal-medical-clinic</t>
@@ -3667,7 +4227,11 @@
           <t>'+971 6 882 8486</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153426/new-zulekha-medical-centre</t>
@@ -3690,7 +4254,11 @@
           <t>'+971 6 558 3351</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18948/riaz-medical-center</t>
@@ -3713,7 +4281,11 @@
           <t>'+971 6 575 0077</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18964/saba-physiotherapy-center</t>
@@ -3736,7 +4308,11 @@
           <t>'+971 6 556 9900</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153829/saudi-german-hospital-group</t>
@@ -3759,7 +4335,11 @@
           <t>'+971 6 573 7888</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18982/scottish-dental-clinic</t>
@@ -3782,7 +4362,11 @@
           <t>'+971 6 538 8966</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153091/sunnys-clinic-dr</t>
@@ -3805,7 +4389,11 @@
           <t>'+971 6 566 2416</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/148778/universal-mediators-fze</t>
@@ -3828,7 +4416,11 @@
           <t>'+971 6 574 4734</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/19059/widex-emirates-hearing-care</t>
@@ -3851,7 +4443,11 @@
           <t>'+971 6 553 8156</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/19073/zulekha-medical-centre</t>
@@ -3874,7 +4470,11 @@
           <t>'+971 6 538 6444</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/342367/al-qassimi-hospital</t>
@@ -3897,7 +4497,11 @@
           <t>'+971 6 538 6444</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153819/al-qasimia-hospital</t>
@@ -3920,7 +4524,11 @@
           <t>'+971 6 511 9000</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/342439/private-rehabilitation-center</t>
@@ -3943,7 +4551,11 @@
           <t>'+971 6 566 0008</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/333696/dr-anwar-pasha-medical-clinic</t>
@@ -3966,7 +4578,11 @@
           <t>'+971 6 562 3151</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153754/abubakar-clinic</t>
@@ -3989,7 +4605,11 @@
           <t>'+971 6 574 0091</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18038/afif-medical-centre</t>
@@ -4012,7 +4632,11 @@
           <t>'+971 6 574 2333</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/152785/ahmed-bishr-medical-centre-dr</t>
@@ -4035,7 +4659,11 @@
           <t>'+971 6 556 8777</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18074/al-amoodi-medical-center</t>
@@ -4058,7 +4686,11 @@
           <t>'+971 6 556 8777</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153495/al-amoodi-medical-centre</t>
@@ -4081,7 +4713,11 @@
           <t>'+971 6 533 1551</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/147633/al-buheira-lacnor-dairies-co-ltd</t>
@@ -4104,7 +4740,11 @@
           <t>'+971 6 533 1894</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/148779/al-fatha-fstuff-trading-co</t>
@@ -4127,7 +4767,11 @@
           <t>'+971 6 561 8825</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18277/alia-clinic</t>
@@ -4150,7 +4794,11 @@
           <t>'+971 6 574 6006</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153752/ali-salem-hindi-clinic-dr</t>
@@ -4173,7 +4821,11 @@
           <t>'+971 6 556 2200</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18146/al-khajah-medical-group</t>
@@ -4196,7 +4848,11 @@
           <t>'+971 6 564 6252</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153349/al-lulu-medical-centre</t>
@@ -4219,7 +4875,11 @@
           <t>'+971 6 543 3772</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/148774/al-maydan-refrigeration</t>
@@ -4242,7 +4902,11 @@
           <t>'+971 6 882 3334</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153757/al-maliha-medical-centre</t>
@@ -4265,7 +4929,11 @@
           <t>'+971 6 556 1610</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18188/al-nawa-medical-centre</t>
@@ -4288,7 +4956,11 @@
           <t>'+971 6 531 5152</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153376/al-nahdah-medical-centre</t>
@@ -4311,7 +4983,11 @@
           <t>'+971 6 573 1735</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18230/al-saraj-medical-centre</t>
@@ -4334,7 +5010,11 @@
           <t>'+971 6 553 8787</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18231/al-sarraf-medical-center</t>
@@ -4357,7 +5037,11 @@
           <t>'+971 6 561 7413</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18233/al-sawami-medical-clinic</t>
@@ -4380,7 +5064,11 @@
           <t>'+971 6 543 2898</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153390/al-safeer-medical-centre</t>
@@ -4403,7 +5091,11 @@
           <t>'+971 6 555 8441</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18252/al-taif-medical-centre</t>
@@ -4426,7 +5118,11 @@
           <t>'+971 6 559 9011</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18262/al-wahda-dental-clinic</t>
@@ -4449,7 +5145,11 @@
           <t>'+971 6 534 6767</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/147646/arla-nfpc</t>
@@ -4472,7 +5172,11 @@
           <t>'+971 6 553 0557</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153292/ashok-menon-clinic-dr</t>
@@ -4495,7 +5199,11 @@
           <t>'+971 6 561 5434</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153508/ayurvedic-herbal-health-centre</t>
@@ -4518,7 +5226,11 @@
           <t>'+971 6 534 1334</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/148783/baras-al-khaimahat-international</t>
@@ -4541,7 +5253,11 @@
           <t>'+971 6 574 6646</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18329/basil-medical-clinic</t>
@@ -4564,7 +5280,11 @@
           <t>'+971 6 562 7778</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/342399/dallas-medical-center</t>
@@ -4587,7 +5307,11 @@
           <t>'+971 6 572 7515</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18401/dental-care-centre</t>
@@ -4610,7 +5334,11 @@
           <t>'+971 6 572 7044</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153375/dhia-h-mahdi-dr</t>
@@ -4633,7 +5361,11 @@
           <t>'+971 6 562 1777</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18411/diana-dental-clinic</t>
@@ -4656,7 +5388,11 @@
           <t>'+971 6 574 2333</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18431/dr-ahmed-bishr-medical-centre</t>
@@ -4679,7 +5415,11 @@
           <t>'+971 6 523 8883</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/342400/dr-amal-al-qedrah-specialist-clinic</t>
@@ -4702,7 +5442,11 @@
           <t>'+971 6 555 1937</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18491/dr-joseph-dental-clinic</t>
@@ -4725,7 +5469,11 @@
           <t>'+971 6 563 6192</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18530/dr-mohd-tharwat-dental-clinic</t>
@@ -4748,7 +5496,11 @@
           <t>'+971 6 562 6525</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18578/dr-sanjay-medical-centre</t>
@@ -4771,7 +5523,11 @@
           <t>'+971 6 533 8732</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18567/dr-sadeq-al-sahaf</t>
@@ -4794,7 +5550,11 @@
           <t>'+971 6 574 2434</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18576/dr-samir-ali-murad-dental-clinic</t>
@@ -4817,7 +5577,11 @@
           <t>'+971 9 238 6389</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153118/east-coast-clinic</t>
@@ -4840,7 +5604,11 @@
           <t>'+971 6 556 3433</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153344/enjab-medical-centre</t>
@@ -4863,7 +5631,11 @@
           <t>'+971 6 562 3722</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18636/esfandyar-polyclinic</t>
@@ -4886,7 +5658,11 @@
           <t>'+971 6 577 5700</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153364/fetal-medicine-clinic</t>
@@ -4909,7 +5685,11 @@
           <t>'+971 6 553 5228</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18666/future-orthodontic-dental-clinic</t>
@@ -4932,7 +5712,11 @@
           <t>'+971 6 575 0280</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18679/german-medical-clinic</t>
@@ -4955,7 +5739,11 @@
           <t>'+971 6 542 3399</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18690/gopi-medical-clinic</t>
@@ -4978,7 +5766,11 @@
           <t>'+971 6 561 6016</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18695/gulf-ayurvedic-centre</t>
@@ -5001,7 +5793,11 @@
           <t>'+971 2 621 7715</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/239069/gulf-medical-projects-company</t>
@@ -5024,7 +5820,11 @@
           <t>'+971 6 572 7767</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153532/habib-dr-ent-clinic</t>
@@ -5047,7 +5847,11 @@
           <t>'+971 6 559 9234</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18709/hakim-medical-center</t>
@@ -5070,7 +5874,11 @@
           <t>'+971 6 562 5634</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18758/jeena-clinic</t>
@@ -5093,7 +5901,11 @@
           <t>'+971 6 555 1937</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153244/joseph-dental-clinic-dr</t>
@@ -5116,7 +5928,11 @@
           <t>'+971 9 277 7002</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153294/kalba-medical-center</t>
@@ -5139,7 +5955,11 @@
           <t>'+971 6 561 8335</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18779/khalid-polyclinic</t>
@@ -5162,7 +5982,11 @@
           <t>'+971 6 559 9828</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18788/knan-dental-clinic</t>
@@ -5185,7 +6009,11 @@
           <t>'+971 6 543 7388</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/147640/kuwait-danish-dairy-co-kcsc-the</t>
@@ -5208,7 +6036,11 @@
           <t>'+971 6 563 0447</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153362/laika-wali-medical-clinic</t>
@@ -5231,7 +6063,11 @@
           <t>'+971 6 533 3951</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153360/legend-clinic</t>
@@ -5254,7 +6090,11 @@
           <t>'+971 6 561 6464</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153527/mampilly-clinic</t>
@@ -5277,7 +6117,11 @@
           <t>'+971 6 568 5557</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153423/mandar-medical-clinic-dr</t>
@@ -5300,7 +6144,11 @@
           <t>'+971 6 544 0555</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/243414/med-pharma</t>
@@ -5323,7 +6171,11 @@
           <t>'+971 6 572 2999</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153332/metawi-medical-paediatrician-clinic</t>
@@ -5346,7 +6198,11 @@
           <t>'+971 6 556 5656</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153384/mohd-a-el-nounou-clinic-dr</t>
@@ -5369,7 +6225,11 @@
           <t>'+971 6 563 6192</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153730/mohd-tharwat-dental-clinic-dr</t>
@@ -5392,7 +6252,11 @@
           <t>'+971 6 553 8238</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153506/mouen-junblat-medical-centre-dr</t>
@@ -5415,7 +6279,11 @@
           <t>'+971 6 573 6500</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/147666/national-agric-dev-co-the</t>
@@ -5438,7 +6306,11 @@
           <t>'+971 6 562 3834</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153394/nathani-clinic</t>
@@ -5461,7 +6333,11 @@
           <t>'+971 6 523 3300</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/342435/national-center-for-modern-medicine</t>
@@ -5484,7 +6360,11 @@
           <t>'+971 6 568 4974</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18905/noor-clinic</t>
@@ -5507,7 +6387,11 @@
           <t>'+971 6 573 7735</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18911/our-own-medical-and-diagnostics-center</t>
@@ -5530,7 +6414,11 @@
           <t>'+971 6 573 7735</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153243/our-own-medicaldiagnostics-center</t>
@@ -5553,7 +6441,11 @@
           <t>'+971 6 557 1797</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/246461/pharmacare-limited</t>
@@ -5576,7 +6468,11 @@
           <t>'+971 6 562 5890</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18928/private-eye-clinic</t>
@@ -5599,7 +6495,11 @@
           <t>'+971 6 573 7789</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153370/psychiatric-clinic</t>
@@ -5622,7 +6522,11 @@
           <t>'+971 6 574 4677</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153366/raad-al-qasik-medical-centre-dr</t>
@@ -5645,7 +6549,11 @@
           <t>'+971 6 572 2330</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153348/rania-al-qedrah-specialized-clinic-dr</t>
@@ -5668,7 +6576,11 @@
           <t>'+971 6 562 0831</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153379/reem-medical-diagnostic-centre</t>
@@ -5691,7 +6603,11 @@
           <t>'+971 6 562 5422</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153729/reem-specialists-medical-center</t>
@@ -5714,7 +6630,11 @@
           <t>'+971 6 561 2900</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18950/rishil-poly-clinic</t>
@@ -5737,7 +6657,11 @@
           <t>'+971 6 533 8732</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153324/sadeq-al-sahaf-dr</t>
@@ -5760,7 +6684,11 @@
           <t>'+971 6 567 6027</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18969/sajida-medical-centre</t>
@@ -5783,7 +6711,11 @@
           <t>'+971 6 553 7007</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153248/samir-abu-zied-clinic-dr</t>
@@ -5806,7 +6738,11 @@
           <t>'+971 6 556 5589</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153357/samia-khedr-medical-clinic-dr</t>
@@ -5829,7 +6765,11 @@
           <t>'+971 6 574 2434</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153760/samir-ali-murad-dental-clinic-dr</t>
@@ -5852,7 +6792,11 @@
           <t>'+971 6 562 6525</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153257/sanjay-medical-centre-dr</t>
@@ -5875,7 +6819,11 @@
           <t>'+971 6 568 2670</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18977/sarhad-medical-clinic</t>
@@ -5898,7 +6846,11 @@
           <t>'+971 6 562 6957</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18978/sasils-dental-clinic</t>
@@ -5921,7 +6873,11 @@
           <t>'+971 6 563 6308</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153824/shakir-s-vali-dr</t>
@@ -5944,7 +6900,11 @@
           <t>'+971 6 561 6556</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153335/solanki-dental-centre</t>
@@ -5967,7 +6927,11 @@
           <t>'+971 6 573 7242</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153356/suha-al-farhan-children-dentist-dr</t>
@@ -5990,7 +6954,11 @@
           <t>'+971 6 573 0666</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/19012/swedish-clinic</t>
@@ -6013,7 +6981,11 @@
           <t>'+971 6 533 9196</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/147639/united-dairies</t>
@@ -6036,7 +7008,11 @@
           <t>'+971 6 568 2258</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153114/venniyil-clinic</t>
@@ -6059,7 +7035,11 @@
           <t>'+971 6 572 1313</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153351/wassim-kabbani-clinic-dr</t>
@@ -6082,7 +7062,11 @@
           <t>'+971 6 577 1757</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153820/wilson-specialized-hospital</t>
@@ -6105,7 +7089,11 @@
           <t>'+971 6 577 1757</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/19052/w-wilson-health-care-group</t>
@@ -6128,7 +7116,11 @@
           <t>'+971 6 538 8205</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18159/al-maliky-dental-clinic</t>
@@ -6147,7 +7139,11 @@
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/226714/al-riyadh-medical-equipments-centre</t>
@@ -6170,7 +7166,11 @@
           <t>'+971 6 568 5022</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18246/al-shrook-polyclinic</t>
@@ -6189,7 +7189,11 @@
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/228491/al-taheal-medical-equipment</t>
@@ -6212,7 +7216,11 @@
           <t>'+971 6 568 7728</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18284/ambegaokar-clinic</t>
@@ -6235,7 +7243,11 @@
           <t>'+971 6 562 0404</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E254" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18397/delta-medical-clinic</t>
@@ -6258,7 +7270,11 @@
           <t>'+971 6 573 6466</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18501/dr-labib-al-hasan-medical-clinic</t>
@@ -6281,7 +7297,11 @@
           <t>'+971 6 561 5754</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18730/hyma-medical-clinic</t>
@@ -6304,7 +7324,11 @@
           <t>'+971 6 561 5754</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153325/hyma-medical-clinic-hemalatha-dr</t>
@@ -6323,7 +7347,11 @@
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/240124/ibn-rushd-medical-drugs-equipment-store</t>
@@ -6346,7 +7374,11 @@
           <t>'+971 6 573 6466</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E259" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153434/labib-al-hasan-medical-clinic-dr</t>
@@ -6369,7 +7401,11 @@
           <t>'+971 6 563 4347</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18839/mediplus-diagnostic-centre</t>
@@ -6392,7 +7428,11 @@
           <t>'+971 9 277 7351</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153411/zafar-dental-clinic</t>
@@ -6415,7 +7455,11 @@
           <t>'+971 6 561 4266</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18091/al-dallah-medical-clinic</t>
@@ -6438,7 +7482,11 @@
           <t>'+971 6 555 1231</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18136/al-jawhara-medical-center</t>
@@ -6461,7 +7509,11 @@
           <t>'+971 6 564 6252</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18150/al-lulu-medical-center</t>
@@ -6484,7 +7536,11 @@
           <t>'+971 6 568 6511</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E265" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18179/al-mushtaq-medical-centre</t>
@@ -6507,7 +7563,11 @@
           <t>'+971 6 538 6444</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E266" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/17633/al-qassemi-hospital</t>
@@ -6530,7 +7590,11 @@
           <t>'+971 6 568 7893</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18209/al-rai-medical-centre</t>
@@ -6553,7 +7617,11 @@
           <t>'+971 6 561 9999</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153809/al-zahra-pvt-hospital</t>
@@ -6576,7 +7644,11 @@
           <t>'+971 6 568 1717</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18333/bhatia-clinic</t>
@@ -6599,7 +7671,11 @@
           <t>'+971 6 563 6552</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18387/dabbous-medical-centre</t>
@@ -6622,7 +7698,11 @@
           <t>'+971 6 572 5626</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18392/davis-dental-clinic</t>
@@ -6645,7 +7725,11 @@
           <t>'+971 6 553 8238</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18532/dr-mouen-junblat-dental-clinic</t>
@@ -6668,7 +7752,11 @@
           <t>'+971 6 574 1313</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18550/dr-oras-sharif-clinic</t>
@@ -6691,7 +7779,11 @@
           <t>'+971 6 572 1919</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18570/dr-said-h-muwafi</t>
@@ -6714,7 +7806,11 @@
           <t>'+971 6 572 2458</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18572/dr-saleh-mohammed-saleh</t>
@@ -6733,7 +7829,11 @@
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/236155/dynamic-rehab-medical-centre</t>
@@ -6756,7 +7856,11 @@
           <t>'+971 6 555 2150</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18650/family-clinic</t>
@@ -6779,7 +7883,11 @@
           <t>'+971 6 561 8300</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18763/jessy-clinic</t>
@@ -6802,7 +7910,11 @@
           <t>'+971 6 561 5307</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18798/lyla-dental-clinic</t>
@@ -6825,7 +7937,11 @@
           <t>'+971 6 568 3405</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18951/rolla-clinic</t>
@@ -6848,7 +7964,11 @@
           <t>'+971 6 563 5201</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18952/romira-paediatric-clinic</t>
@@ -6871,7 +7991,11 @@
           <t>'+971 6 573 6800</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/19006/specialized-medical-center</t>
@@ -6894,7 +8018,11 @@
           <t>'+971 6 572 4484</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18468/dr-gills-clinic</t>
@@ -6913,7 +8041,11 @@
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/218254/al-ameen-medical-centre</t>
@@ -6936,7 +8068,11 @@
           <t>'+971 6 555 1981</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/152776/assi-dental-clinic-dr</t>
@@ -6959,7 +8095,11 @@
           <t>'+971 6 538 6444</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E286" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153808/new-al-qassemiya-hospital</t>
@@ -6982,7 +8122,11 @@
           <t>'+971 6 542 0066</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E287" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/364526/modern-clinic</t>
@@ -7005,7 +8149,11 @@
           <t>'+971 6 573 3440</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E288" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153339/abdulla-semrin-clinic-dr</t>
@@ -7028,7 +8176,11 @@
           <t>'+971 6 555 1231</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr"/>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E289" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153504/adnan-ballout-clinic-dr</t>
@@ -7051,7 +8203,11 @@
           <t>'+971 6 556 1220</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E290" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18036/advanced-eye-clinic</t>
@@ -7074,7 +8230,11 @@
           <t>'+971 6 562 1700</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18059/al-ahlia-regional-medical-centre</t>
@@ -7097,7 +8257,11 @@
           <t>'+971 6 561 5545</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18071/al-amanah-medical-centre</t>
@@ -7120,7 +8284,11 @@
           <t>'+971 6 561 6828</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr"/>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E293" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/152760/al-ansari-clinic</t>
@@ -7143,7 +8311,11 @@
           <t>'+971 6 534 8384</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/302790/al-araimi-gen-trading-llc</t>
@@ -7166,7 +8338,11 @@
           <t>'+971 6 555 9905</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/333726/al-alfiah-dental-clinic</t>
@@ -7189,7 +8365,11 @@
           <t>'+971 6 543 1763</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18085/al-barakah-medical-clinic</t>
@@ -7212,7 +8392,11 @@
           <t>'+971 6 543 1763</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/152771/al-baras-al-khaimahah-medical-clinic</t>
@@ -7235,7 +8419,11 @@
           <t>'+971 6 572 7175</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153105/al-batool-complex-medical</t>
@@ -7258,7 +8446,11 @@
           <t>'+971 6 533 6176</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18095/al-darary-medical-centre</t>
@@ -7281,7 +8473,11 @@
           <t>'+971 6 532 0800</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153731/al-diyafah-medical-centre</t>
@@ -7304,7 +8500,11 @@
           <t>'+971 6 534 3870</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/331951/al-fanar-food-industries-llc</t>
@@ -7327,7 +8527,11 @@
           <t>'+971 6 556 2444</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/152778/al-huda-polyclinic</t>
@@ -7350,7 +8554,11 @@
           <t>'+971 6 561 3613</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18128/al-ishraf-medical-centre</t>
@@ -7373,7 +8581,11 @@
           <t>'+971 6 561 3613</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153305/al-ishraf-medical-center</t>
@@ -7396,7 +8608,11 @@
           <t>'+971 6 556 5660</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr"/>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18156/al-majaz-medical-centre</t>
@@ -7419,7 +8635,11 @@
           <t>'+971 6 573 9545</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18176/al-muntasir-medical-centre</t>
@@ -7442,7 +8662,11 @@
           <t>'+971 6 538 8205</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E307" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18160/al-maliky-dental-clinic</t>
@@ -7465,7 +8689,11 @@
           <t>'+971 4 338 3339</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E308" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/224696/al-mufid-trading-company-llc</t>
@@ -7488,7 +8716,11 @@
           <t>'+971 6 561 8899</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18185/al-nakheel-medical-centre</t>
@@ -7511,7 +8743,11 @@
           <t>'+971 6 561 2696</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr"/>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18181/al-naeem-medical-center</t>
@@ -7534,7 +8770,11 @@
           <t>'+971 6 533 4415</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr"/>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18204/al-raha-medical-center</t>
@@ -7557,7 +8797,11 @@
           <t>'+971 6 533 3913</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/318786/al-rubiyan-trading-company-llc</t>
@@ -7580,7 +8824,11 @@
           <t>'+971 6 557 5075</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/332063/al-rimal-foodstuff-inds-fzc</t>
@@ -7603,7 +8851,11 @@
           <t>'+971 6 562 3949</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr"/>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18218/al-saadah-medical-center</t>
@@ -7626,7 +8878,11 @@
           <t>'+971 6 563 5211</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18219/al-safa-clinic</t>
@@ -7649,7 +8905,11 @@
           <t>'+971 6 563 2618</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18223/al-saha-wa-al-shifaa-specialities-complex</t>
@@ -7672,7 +8932,11 @@
           <t>'+971 6 532 5327</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/148788/al-shams-food-industries</t>
@@ -7695,7 +8959,11 @@
           <t>'+971(6)379735</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/299592/al-shulla-vet-center</t>
@@ -7718,7 +8986,11 @@
           <t>'+971 6 563 2618</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr"/>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/333639/al-soha-and-al-shifa-specialities-complex</t>
@@ -7741,7 +9013,11 @@
           <t>'+971 6 572 7757</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153338/al-thequah-clinic</t>
@@ -7764,7 +9040,11 @@
           <t>'+971 6 534 7494</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18259/al-wafir-medical-centre</t>
@@ -7787,7 +9067,11 @@
           <t>'+971 6 574 9666</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18266/al-widad-specialist-clinic</t>
@@ -7810,7 +9094,11 @@
           <t>'+971 6 574 9666</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr"/>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E323" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/333683/al-widad-specialist</t>
@@ -7833,7 +9121,11 @@
           <t>'+971 6 561 9999</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/299495/al-zahar-hospital</t>
@@ -7856,7 +9148,11 @@
           <t>'+971 6 556 5564</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18282/amal-abdel-kader-dental-clinic</t>
@@ -7879,7 +9175,11 @@
           <t>'+971 6 563 0555</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr"/>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E326" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18299/anthony-medical-centre</t>
@@ -7902,7 +9202,11 @@
           <t>'+971 6 563 0555</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/152770/antony-medical-centre</t>
@@ -7925,7 +9229,11 @@
           <t>'+971 6 538 7199</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18301/apollo-medical-clinic</t>
@@ -7948,7 +9256,11 @@
           <t>'+971 6 574 8290</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr"/>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/232623/baniyas-medical-equipment-trading</t>
@@ -7971,7 +9283,11 @@
           <t>'+971 6 532 8558</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr"/>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E330" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/333644/bilal-medical-centre</t>
@@ -7994,7 +9310,11 @@
           <t>'+971 6 562 0181</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr"/>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E331" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153272/chithra-shamsudheens-clinic-dr</t>
@@ -8017,7 +9337,11 @@
           <t>'+971 6 568 5466</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153734/chinese-clinic-the</t>
@@ -8040,7 +9364,11 @@
           <t>'+971 6 524 3444</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr"/>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E333" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18372/cocoon-individualized-natal-care</t>
@@ -8063,7 +9391,11 @@
           <t>'+971 6 533 5555</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18376/consultant-polymedic</t>
@@ -8086,7 +9418,11 @@
           <t>'+971 6 561 8801</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr"/>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E335" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/333736/derma-health</t>
@@ -8109,7 +9445,11 @@
           <t>'+971 6 558 4335</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E336" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18408/deva-medical-centre</t>
@@ -8132,7 +9472,11 @@
           <t>'+971 6 562 0181</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr"/>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E337" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18453/dr-chithra-shamsudheens-clinic</t>
@@ -8155,7 +9499,11 @@
           <t>'+971 6 561 6261</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18506/dr-maged-salah-eldin</t>
@@ -8178,7 +9526,11 @@
           <t>'+971 6 573 9899</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18515/dr-mariyam-dental-clinic</t>
@@ -8201,7 +9553,11 @@
           <t>'+971 6 555 2116</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18525/dr-mohd-ahmed-ali-dental-clinic</t>
@@ -8224,7 +9580,11 @@
           <t>'+971 6 556 5568</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18551/dr-rabha-habib-el-sayegh-clinic</t>
@@ -8247,7 +9607,11 @@
           <t>'+971 6 569 0569</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18558/dr-ravindran-gopal-clinic</t>
@@ -8270,7 +9634,11 @@
           <t>'+971 6 555 1666</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/152775/emirates-pvt-poly-clinic</t>
@@ -8293,7 +9661,11 @@
           <t>'+971 6 573 6866</t>
         </is>
       </c>
-      <c r="D344" t="inlineStr"/>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/236644/emirates-medical-lab</t>
@@ -8316,7 +9688,11 @@
           <t>'+971 6 556 3433</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/333741/enjab-hospital-for-day-care</t>
@@ -8339,7 +9715,11 @@
           <t>'+971 6 556 0002</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr"/>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E346" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153409/ent-specialized-clinic</t>
@@ -8362,7 +9742,11 @@
           <t>'+971 6 559 1110</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr"/>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E347" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153112/gayatree-medical-centre</t>
@@ -8385,7 +9769,11 @@
           <t>'+971 6 568 5620</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr"/>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E348" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153117/hayat-medical-centre</t>
@@ -8408,7 +9796,11 @@
           <t>'+971 6 563 5029</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E349" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153308/hejazis-clinic-dr</t>
@@ -8431,7 +9823,11 @@
           <t>'+971 6 568 7000</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E350" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153438/islamic-medical-herbs-treatment-center</t>
@@ -8454,7 +9850,11 @@
           <t>'+971 6 568 7255</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E351" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/240841/ismail-mohd-al-nimir</t>
@@ -8477,7 +9877,11 @@
           <t>'+971 6 572 4855</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr"/>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E352" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153361/jwan-s-murad-clinic-dr</t>
@@ -8500,7 +9904,11 @@
           <t>'+971 6 562 4725</t>
         </is>
       </c>
-      <c r="D353" t="inlineStr"/>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E353" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153249/kottakkal-health-massage</t>
@@ -8523,7 +9931,11 @@
           <t>'+971 6 561 6261</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153746/maged-salah-el-din-clinic-dr</t>
@@ -8546,7 +9958,11 @@
           <t>'+971 6 572 6272</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153371/malek-a-nawas-dr</t>
@@ -8569,7 +9985,11 @@
           <t>'+971 6 572 6272</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153387/malek-abdulla-nawas-dr</t>
@@ -8592,7 +10012,11 @@
           <t>'+971 6 568 5557</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/333664/mandar-medical-centre</t>
@@ -8615,7 +10039,11 @@
           <t>'+971 6 573 9899</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E358" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153262/mariyam-dental-clinic-dr</t>
@@ -8638,7 +10066,11 @@
           <t>'+971 6 572 2999</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr"/>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E359" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153381/metawi-medical-clinic</t>
@@ -8661,7 +10093,11 @@
           <t>'+971 6 574 9610</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr"/>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E360" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/333734/minal-specialised-clinic-dermatology</t>
@@ -8684,7 +10120,11 @@
           <t>'+971 6 555 2116</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr"/>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E361" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153510/mohd-ahamad-ali-dental-clinic-dr</t>
@@ -8707,7 +10147,11 @@
           <t>'+971 6 561 7755</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr"/>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E362" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153331/mount-seena-medical-centre</t>
@@ -8730,7 +10174,11 @@
           <t>'+971(6)384166</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E363" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/299599/nadd-al-shiba-vet-clinic</t>
@@ -8753,7 +10201,11 @@
           <t>'+971 6 534 6522</t>
         </is>
       </c>
-      <c r="D364" t="inlineStr"/>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>kiwavix919@dwseal.co</t>
+        </is>
+      </c>
       <c r="E364" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/333669/nanda-medical-centre</t>

--- a/yello_doctor_sharjah.xlsx
+++ b/yello_doctor_sharjah.xlsx
@@ -459,11 +459,7 @@
           <t>'+971 6 565 0690</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/344092/al-abqari-dental-clinic</t>
@@ -486,11 +482,7 @@
           <t>'+971 6 561 7822</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>info@vedhansh.com</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/351899/austin-center-for-rehabilitation-of-person-with-disabilities</t>
@@ -513,11 +505,7 @@
           <t>'+971 6 566 7996</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/354307/sunny-sharqan-medical-centre</t>
@@ -540,11 +528,7 @@
           <t>'+971 6 559 0007</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/352212/al-afdal-medical-center</t>
@@ -567,11 +551,7 @@
           <t>'+971 6 525 3756</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/356351/mulk-physiotherapy-center</t>
@@ -594,11 +574,7 @@
           <t>'+971 6 550 3558</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/343954/ibtisamty-dental-clinic</t>
@@ -621,11 +597,7 @@
           <t>'+971 6 521 8889</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/374124/shifa-al-jazeera-medical-centre-llc</t>
@@ -648,11 +620,7 @@
           <t>'+971 6 506 0000</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/17710/zulekha-hospital</t>
@@ -675,11 +643,7 @@
           <t>'+971 6 566 7661</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>alamumahmc@gmail.com</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/352120/dr-uma-maheswari</t>
@@ -702,11 +666,7 @@
           <t>'+971 6 559 1985</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/349515/al-elaj-medical-equipment-tr</t>
@@ -729,11 +689,7 @@
           <t>'+971 6 526 6885</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/347642/art-medical-center</t>
@@ -756,11 +712,7 @@
           <t>'+971 6 568 8600</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/358083/asala-medical-center</t>
@@ -783,11 +735,7 @@
           <t>'+971 6 567 1707</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/347083/al-bawadi-medicaldiagnostic-center</t>
@@ -810,11 +758,7 @@
           <t>'+971 6 555 1575</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/355131/right-medical-centre</t>
@@ -837,11 +781,7 @@
           <t>'+971 6 561 2737</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18028/abrahams-medical-centre</t>
@@ -864,11 +804,7 @@
           <t>'+971 6 530 6161</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/362487/ahlan-medical-center</t>
@@ -891,11 +827,7 @@
           <t>'+971 6 553 0557</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18451/dr-ashok-menon-clinic</t>
@@ -918,11 +850,7 @@
           <t>'+971 6 574 4529</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18042/ahalia-medical-centre</t>
@@ -945,11 +873,7 @@
           <t>'+971 6 535 3582</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/342387/al-shams-medicaldiagnostic-centre</t>
@@ -972,11 +896,7 @@
           <t>'+971 6 557 1132</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/207709/bentham-science-publishers-ltd-fzc</t>
@@ -999,11 +919,7 @@
           <t>'+971 6 573 7005</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>info@bissanmc.com</t>
-        </is>
-      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153264/bissam-medical-centre</t>
@@ -1026,11 +942,7 @@
           <t>'+971 6 522 4422</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/359495/california-dental-clinic</t>
@@ -1053,11 +965,7 @@
           <t>'+971 6 565 2332</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18370/class-medical-centre</t>
@@ -1080,11 +988,7 @@
           <t>'+971 6 575 2200</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18924/prime-medical-center-sharjah</t>
@@ -1107,11 +1011,7 @@
           <t>'+971 6 562 5234</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153395/yathish-kamath-dr-mds-marina-medical-centre</t>
@@ -1134,11 +1034,7 @@
           <t>'+971 6 562 3151</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18032/abubakr-clinic</t>
@@ -1161,11 +1057,7 @@
           <t>'+971 50 424 9032</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/367437/adam-veterinary-medicines-llc</t>
@@ -1188,11 +1080,7 @@
           <t>'+971 6 556 2200</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/222958/al-khaja-medical-clinic</t>
@@ -1215,11 +1103,7 @@
           <t>'+971 6 563 2618</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/361038/al-saha-al-shifa</t>
@@ -1242,11 +1126,7 @@
           <t>'+971 6 575 3888</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/17647/bhatia-medical-centre</t>
@@ -1269,11 +1149,7 @@
           <t>'+971 6 563 2100</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18416/doctors-medical-centre</t>
@@ -1296,11 +1172,7 @@
           <t>'+971 52 277 5005</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/364544/dr-zains-homeopathic-clinic-sharjah</t>
@@ -1323,11 +1195,7 @@
           <t>'+971 6 530 9898</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/367702/elite-medical-center</t>
@@ -1350,11 +1218,7 @@
           <t>'+971 6 518 0800</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/362215/ishaq-bin-omran-medical-center-ibo</t>
@@ -1377,11 +1241,7 @@
           <t>'+971 6 525 1000</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/347798/oriana-hospital</t>
@@ -1404,11 +1264,7 @@
           <t>'+971 6 568 2258</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/25748/venniyil-medical-centre</t>
@@ -1431,11 +1287,7 @@
           <t>'+971 6 534 4439</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18143/al-kanary-medical-clinic</t>
@@ -1458,11 +1310,7 @@
           <t>'+971 6 505 7048</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/341538/university-hospital-sharjah</t>
@@ -1485,11 +1333,7 @@
           <t>'+971 600520057</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/371303/hygiene-fresh</t>
@@ -1512,11 +1356,7 @@
           <t>'+971 6 566 7661</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/352098/al-amumah-medical-center</t>
@@ -1539,11 +1379,7 @@
           <t>'+971 6 530 4900</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/353173/lifeway-specialized-medical-centre</t>
@@ -1566,11 +1402,7 @@
           <t>'+971 6 566 8745</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18875/nahar-mampilly-medical-centre</t>
@@ -1593,11 +1425,7 @@
           <t>'+971 6 533 7864</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/148789/unipex-dairy-products-co-ltd</t>
@@ -1620,11 +1448,7 @@
           <t>'+971 6 556 9888</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/350245/al-durrah-radiology-center</t>
@@ -1647,11 +1471,7 @@
           <t>'+971 6 569 1791</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/19188/al-watania-veterinary-clinic</t>
@@ -1674,11 +1494,7 @@
           <t>'+971 6 882 2270</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/349667/al-ysra-medical-center</t>
@@ -1701,11 +1517,7 @@
           <t>'+971 6 524 5444</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18380/cosme-surge</t>
@@ -1728,11 +1540,7 @@
           <t>'+971 50 860 6857</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/19201/europets-hospital</t>
@@ -1755,11 +1563,7 @@
           <t>'+971 6 534 3803</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/319890/grade-refrigeration-llc</t>
@@ -1782,11 +1586,7 @@
           <t>'+971 6 509 5555</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/371813/gulf-medical-projects</t>
@@ -1809,11 +1609,7 @@
           <t>'+971 6 518 0800</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/360000/ibo</t>
@@ -1836,11 +1632,7 @@
           <t>'+971 6 530 4900</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/366850/lifeway-specialized-medical-centre</t>
@@ -1863,11 +1655,7 @@
           <t>'+971 50 963 8577</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/361312/best-gynaecologist-in-uae</t>
@@ -1890,11 +1678,7 @@
           <t>'+971 6 573 8088</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/333177/international-radiology-centre</t>
@@ -1917,11 +1701,7 @@
           <t>'+971 6 525 4446</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/362584/new-hope-ivf</t>
@@ -1944,11 +1724,7 @@
           <t>'+971 6 561 5545</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18070/al-amanah-medical-centre</t>
@@ -1971,11 +1747,7 @@
           <t>'+971 6 561 7277</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18155/al-mahmood-medical-centre</t>
@@ -1998,11 +1770,7 @@
           <t>'+971 6 561 4262</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18224/al-salam-clinic</t>
@@ -2025,11 +1793,7 @@
           <t>'+971 50 252 5966</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/373035/al-sherouq-medical-center</t>
@@ -2052,11 +1816,7 @@
           <t>'+971 6 556 3969</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/373835/al-safwa-radiology-center</t>
@@ -2079,11 +1839,7 @@
           <t>'+971 6 563 6308</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/17650/central-private-hospital</t>
@@ -2106,11 +1862,7 @@
           <t>'+971 56 563 6802</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/357446/desert-mart</t>
@@ -2133,11 +1885,7 @@
           <t>'+971 6 555 1666</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18635/emirates-private-poly-clinic</t>
@@ -2160,11 +1908,7 @@
           <t>'+971 6 572 5551</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/365301/eve-fertility-center</t>
@@ -2187,11 +1931,7 @@
           <t>'+971 6 574 4266</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18661/french-rheumatism-clinic</t>
@@ -2214,11 +1954,7 @@
           <t>'+971 50 963 8577</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/363115/gynaecologist-in-sharjah</t>
@@ -2241,11 +1977,7 @@
           <t>'+971 6 539 4466</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/241300/julphar-drug-store-sharjah</t>
@@ -2268,11 +2000,7 @@
           <t>'+971 6 565 2929</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/360495/medical-center-in-sharjah</t>
@@ -2295,11 +2023,7 @@
           <t>'+971 6 574 9610</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18850/minal-medical-clinic</t>
@@ -2322,11 +2046,7 @@
           <t>'+971 6 568 6200</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18880/nathani-medical-centre</t>
@@ -2349,11 +2069,7 @@
           <t>'+971 6 553 6936</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18896/new-medical-centre</t>
@@ -2376,11 +2092,7 @@
           <t>'+971 6 562 5422</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18943/reem-specialists-medical-centre</t>
@@ -2403,11 +2115,7 @@
           <t>'+971 6 558 1515</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/17691/royal-hospital</t>
@@ -2430,11 +2138,7 @@
           <t>'+971 6 575 1222</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/17696/sharjah-corniche-hospital</t>
@@ -2457,11 +2161,7 @@
           <t>'+971 6 561 6556</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/19000/solanki-dental-center</t>
@@ -2484,11 +2184,7 @@
           <t>'+971 6 530 5882</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18047/ahlan-dental-clinic</t>
@@ -2511,11 +2207,7 @@
           <t>'+971 6 555 1981</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18555/dr-ramzi-assi-dental-clinic</t>
@@ -2538,11 +2230,7 @@
           <t>'+971 6 557 0722</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/147645/al-ain-farms-for-livestock-production</t>
@@ -2565,11 +2253,7 @@
           <t>'+971 6 561 3030</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/348714/optimum-medical-center</t>
@@ -2592,11 +2276,7 @@
           <t>'+971 4 323 1889</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/371138/dermahealth</t>
@@ -2615,11 +2295,7 @@
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18770/jwan-murad-fertility-clinic</t>
@@ -2642,11 +2318,7 @@
           <t>'+971 6 556 2727</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/152772/abdul-ghani-siddique-ent-clinic-dr</t>
@@ -2669,11 +2341,7 @@
           <t>'+971 6 562 1700</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18057/al-ahalia-regional-medical-centre</t>
@@ -2696,11 +2364,7 @@
           <t>'+971 6 559 9699</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18089/al-buhairah-medical-centre</t>
@@ -2723,11 +2387,7 @@
           <t>'+971 6 559 9147</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/19179/al-faseel-veterinarypet-clinic</t>
@@ -2750,11 +2410,7 @@
           <t>'+971 6 562 4456</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18130/al-jahharah-dental-clinic</t>
@@ -2777,11 +2433,7 @@
           <t>'+971 6 561 7577</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18280/alpha-medical-centre</t>
@@ -2804,11 +2456,7 @@
           <t>'+971 6 538 9999</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/228848/al-thiqah-club-for-handicapped</t>
@@ -2831,11 +2479,7 @@
           <t>'+971 6 559 4454</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18296/annie-dental-clinic</t>
@@ -2858,11 +2502,7 @@
           <t>'+971 6 557 3559</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/147655/aqsa-international-fzc</t>
@@ -2885,11 +2525,7 @@
           <t>'+971 6 530 3999</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/361501/best-physiotherapy-clinic-in-sharjah</t>
@@ -2912,11 +2548,7 @@
           <t>'+971 6 559 2930</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18388/dablan-dental-clinic</t>
@@ -2939,11 +2571,7 @@
           <t>'+971 6 574 6006</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18437/dr-ali-salem-hindi-clinic</t>
@@ -2966,11 +2594,7 @@
           <t>'+971 6 572 7700</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18449/dr-asad-i-dajani-specialized-centre</t>
@@ -2993,11 +2617,7 @@
           <t>'+971 6 559 1110</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18464/dr-gayatree-medical-centre</t>
@@ -3020,11 +2640,7 @@
           <t>'+971 6 572 7767</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18469/dr-habib-ear-nosethroat-clinic</t>
@@ -3047,11 +2663,7 @@
           <t>'+971 6 563 5029</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18475/dr-hijazis-clinic</t>
@@ -3074,11 +2686,7 @@
           <t>'+971 6 568 5557</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18513/dr-mandar-medical-clinic</t>
@@ -3101,11 +2709,7 @@
           <t>'+971 6 572 1052</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18546/dr-nemat-mossalami</t>
@@ -3128,11 +2732,7 @@
           <t>'+971 6 553 7007</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18575/dr-samir-abou-zeid-clinic</t>
@@ -3155,11 +2755,7 @@
           <t>'+971 6 573 7242</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18590/dr-suha-al-farhan-clinic</t>
@@ -3182,11 +2778,7 @@
           <t>'+971 6 563 9966</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18592/dr-sunny-medical-centre</t>
@@ -3209,11 +2801,7 @@
           <t>'+971 6 562 3844</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18740/ideal-medical-centre</t>
@@ -3236,11 +2824,7 @@
           <t>'+971 6 559 5285</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18746/indulekha-medical-clinic</t>
@@ -3263,11 +2847,7 @@
           <t>'+971 6 524 2688</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18762/jennifer-skin-care-centre</t>
@@ -3290,11 +2870,7 @@
           <t>'+971 6 561 6464</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18810/mampilly-eye-clinic</t>
@@ -3317,11 +2893,7 @@
           <t>'+971 6 569 1400</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18817/marijeh-clinic</t>
@@ -3344,11 +2916,7 @@
           <t>'+971 6 562 5234</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18819/marina-medical-centre</t>
@@ -3371,11 +2939,7 @@
           <t>'+971 6 563 7719</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18831/medical-house-for-diagnosistreatment</t>
@@ -3398,11 +2962,7 @@
           <t>'+971 6 562 6922</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18836/medicare-clinic</t>
@@ -3425,11 +2985,7 @@
           <t>'+971 6 539 6200</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18841/mega-medical-centre</t>
@@ -3452,11 +3008,7 @@
           <t>'+971 6 533 9799</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18855/modern-dental-clinic</t>
@@ -3479,11 +3031,7 @@
           <t>'+971 6 561 5111</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18954/roy-dental-clinic</t>
@@ -3506,11 +3054,7 @@
           <t>'+971 6 555 3355</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18962/russian-medicalscientific-complex</t>
@@ -3533,11 +3077,7 @@
           <t>'+971 6 556 8888</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18976/sara-medical-centre</t>
@@ -3560,11 +3100,7 @@
           <t>'+971 6 553 1080</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18986/shamma-dental-clinic</t>
@@ -3587,11 +3123,7 @@
           <t>'+971 6 530 5252</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/342444/sunny-al-nahda-medical-centre</t>
@@ -3614,11 +3146,7 @@
           <t>'+971 55 390 8860</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/342445/sunny-speciality-medical-center</t>
@@ -3641,11 +3169,7 @@
           <t>'+971 6 568 2258</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/19049/venniyil-medical-centre</t>
@@ -3668,11 +3192,7 @@
           <t>'+971 6 533 3949</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/19070/ziad-e-baghdan-clinic</t>
@@ -3695,11 +3215,7 @@
           <t>'+971 6 530 3999</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/363079/cure-medical-center-physiotherapy</t>
@@ -3722,11 +3238,7 @@
           <t>'+971 6 524 2111</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/17673/kuwaiti-hospital</t>
@@ -3749,11 +3261,7 @@
           <t>'+971 55 551 2478</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/369118/yalla-doc</t>
@@ -3776,11 +3284,7 @@
           <t>'+971 6 563 1429</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18173/al-mueed-clinic</t>
@@ -3803,11 +3307,7 @@
           <t>'+971 6 561 9999</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/17640/al-zahra-private-hospital</t>
@@ -3826,11 +3326,7 @@
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/317241/cpr-select</t>
@@ -3849,11 +3345,7 @@
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/368316/niyana</t>
@@ -3876,11 +3368,7 @@
           <t>'+971 6 561 2737</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153514/abrahams-medical-clinic</t>
@@ -3903,11 +3391,7 @@
           <t>'+971 6 886 1202</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/342379/al-faiez-medical-clinic</t>
@@ -3930,11 +3414,7 @@
           <t>'+971 6 561 7277</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/152788/al-mahmoud-medical-centre</t>
@@ -3957,11 +3437,7 @@
           <t>'+971 6 542 4255</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18237/al-shams-medical-centre</t>
@@ -3984,11 +3460,7 @@
           <t>'+971 6 535 3581</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/342388/al-shams-medical-group</t>
@@ -4011,11 +3483,7 @@
           <t>'+971 6 539 7539</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/342395/amritha-medical-centre</t>
@@ -4038,11 +3506,7 @@
           <t>'+971 6 544 4666</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/342396/berlin-medical-centre</t>
@@ -4065,11 +3529,7 @@
           <t>'+971 6 563 9900</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153810/central-pvt-hospital</t>
@@ -4092,11 +3552,7 @@
           <t>'+971 6 577 1822</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18375/conceive-the-gynaecologyfertility-centre</t>
@@ -4119,11 +3575,7 @@
           <t>'+971 6 533 5555</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/152782/consultants-polymedic</t>
@@ -4146,11 +3598,7 @@
           <t>'+971 6 577 1822</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153131/conceive</t>
@@ -4173,11 +3621,7 @@
           <t>'+971 55 587 9093</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/368791/merlin-life-sciences</t>
@@ -4200,11 +3644,7 @@
           <t>'+971 6 574 9610</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18851/minal-medical-clinic</t>
@@ -4227,11 +3667,7 @@
           <t>'+971 6 882 8486</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153426/new-zulekha-medical-centre</t>
@@ -4254,11 +3690,7 @@
           <t>'+971 6 558 3351</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18948/riaz-medical-center</t>
@@ -4281,11 +3713,7 @@
           <t>'+971 6 575 0077</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18964/saba-physiotherapy-center</t>
@@ -4308,11 +3736,7 @@
           <t>'+971 6 556 9900</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153829/saudi-german-hospital-group</t>
@@ -4335,11 +3759,7 @@
           <t>'+971 6 573 7888</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18982/scottish-dental-clinic</t>
@@ -4362,11 +3782,7 @@
           <t>'+971 6 538 8966</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153091/sunnys-clinic-dr</t>
@@ -4389,11 +3805,7 @@
           <t>'+971 6 566 2416</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/148778/universal-mediators-fze</t>
@@ -4416,11 +3828,7 @@
           <t>'+971 6 574 4734</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/19059/widex-emirates-hearing-care</t>
@@ -4443,11 +3851,7 @@
           <t>'+971 6 553 8156</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/19073/zulekha-medical-centre</t>
@@ -4470,11 +3874,7 @@
           <t>'+971 6 538 6444</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/342367/al-qassimi-hospital</t>
@@ -4497,11 +3897,7 @@
           <t>'+971 6 538 6444</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153819/al-qasimia-hospital</t>
@@ -4524,11 +3920,7 @@
           <t>'+971 6 511 9000</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/342439/private-rehabilitation-center</t>
@@ -4551,11 +3943,7 @@
           <t>'+971 6 566 0008</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/333696/dr-anwar-pasha-medical-clinic</t>
@@ -4578,11 +3966,7 @@
           <t>'+971 6 562 3151</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153754/abubakar-clinic</t>
@@ -4605,11 +3989,7 @@
           <t>'+971 6 574 0091</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18038/afif-medical-centre</t>
@@ -4632,11 +4012,7 @@
           <t>'+971 6 574 2333</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/152785/ahmed-bishr-medical-centre-dr</t>
@@ -4659,11 +4035,7 @@
           <t>'+971 6 556 8777</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18074/al-amoodi-medical-center</t>
@@ -4686,11 +4058,7 @@
           <t>'+971 6 556 8777</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153495/al-amoodi-medical-centre</t>
@@ -4713,11 +4081,7 @@
           <t>'+971 6 533 1551</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/147633/al-buheira-lacnor-dairies-co-ltd</t>
@@ -4740,11 +4104,7 @@
           <t>'+971 6 533 1894</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/148779/al-fatha-fstuff-trading-co</t>
@@ -4767,11 +4127,7 @@
           <t>'+971 6 561 8825</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18277/alia-clinic</t>
@@ -4794,11 +4150,7 @@
           <t>'+971 6 574 6006</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153752/ali-salem-hindi-clinic-dr</t>
@@ -4821,11 +4173,7 @@
           <t>'+971 6 556 2200</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18146/al-khajah-medical-group</t>
@@ -4848,11 +4196,7 @@
           <t>'+971 6 564 6252</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153349/al-lulu-medical-centre</t>
@@ -4875,11 +4219,7 @@
           <t>'+971 6 543 3772</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/148774/al-maydan-refrigeration</t>
@@ -4902,11 +4242,7 @@
           <t>'+971 6 882 3334</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153757/al-maliha-medical-centre</t>
@@ -4929,11 +4265,7 @@
           <t>'+971 6 556 1610</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18188/al-nawa-medical-centre</t>
@@ -4956,11 +4288,7 @@
           <t>'+971 6 531 5152</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153376/al-nahdah-medical-centre</t>
@@ -4983,11 +4311,7 @@
           <t>'+971 6 573 1735</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18230/al-saraj-medical-centre</t>
@@ -5010,11 +4334,7 @@
           <t>'+971 6 553 8787</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18231/al-sarraf-medical-center</t>
@@ -5037,11 +4357,7 @@
           <t>'+971 6 561 7413</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18233/al-sawami-medical-clinic</t>
@@ -5064,11 +4380,7 @@
           <t>'+971 6 543 2898</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153390/al-safeer-medical-centre</t>
@@ -5091,11 +4403,7 @@
           <t>'+971 6 555 8441</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18252/al-taif-medical-centre</t>
@@ -5118,11 +4426,7 @@
           <t>'+971 6 559 9011</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18262/al-wahda-dental-clinic</t>
@@ -5145,11 +4449,7 @@
           <t>'+971 6 534 6767</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/147646/arla-nfpc</t>
@@ -5172,11 +4472,7 @@
           <t>'+971 6 553 0557</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153292/ashok-menon-clinic-dr</t>
@@ -5199,11 +4495,7 @@
           <t>'+971 6 561 5434</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153508/ayurvedic-herbal-health-centre</t>
@@ -5226,11 +4518,7 @@
           <t>'+971 6 534 1334</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/148783/baras-al-khaimahat-international</t>
@@ -5253,11 +4541,7 @@
           <t>'+971 6 574 6646</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18329/basil-medical-clinic</t>
@@ -5280,11 +4564,7 @@
           <t>'+971 6 562 7778</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/342399/dallas-medical-center</t>
@@ -5307,11 +4587,7 @@
           <t>'+971 6 572 7515</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18401/dental-care-centre</t>
@@ -5334,11 +4610,7 @@
           <t>'+971 6 572 7044</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153375/dhia-h-mahdi-dr</t>
@@ -5361,11 +4633,7 @@
           <t>'+971 6 562 1777</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18411/diana-dental-clinic</t>
@@ -5388,11 +4656,7 @@
           <t>'+971 6 574 2333</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18431/dr-ahmed-bishr-medical-centre</t>
@@ -5415,11 +4679,7 @@
           <t>'+971 6 523 8883</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/342400/dr-amal-al-qedrah-specialist-clinic</t>
@@ -5442,11 +4702,7 @@
           <t>'+971 6 555 1937</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18491/dr-joseph-dental-clinic</t>
@@ -5469,11 +4725,7 @@
           <t>'+971 6 563 6192</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18530/dr-mohd-tharwat-dental-clinic</t>
@@ -5496,11 +4748,7 @@
           <t>'+971 6 562 6525</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18578/dr-sanjay-medical-centre</t>
@@ -5523,11 +4771,7 @@
           <t>'+971 6 533 8732</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18567/dr-sadeq-al-sahaf</t>
@@ -5550,11 +4794,7 @@
           <t>'+971 6 574 2434</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18576/dr-samir-ali-murad-dental-clinic</t>
@@ -5577,11 +4817,7 @@
           <t>'+971 9 238 6389</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153118/east-coast-clinic</t>
@@ -5604,11 +4840,7 @@
           <t>'+971 6 556 3433</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153344/enjab-medical-centre</t>
@@ -5631,11 +4863,7 @@
           <t>'+971 6 562 3722</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18636/esfandyar-polyclinic</t>
@@ -5658,11 +4886,7 @@
           <t>'+971 6 577 5700</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153364/fetal-medicine-clinic</t>
@@ -5685,11 +4909,7 @@
           <t>'+971 6 553 5228</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18666/future-orthodontic-dental-clinic</t>
@@ -5712,11 +4932,7 @@
           <t>'+971 6 575 0280</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18679/german-medical-clinic</t>
@@ -5739,11 +4955,7 @@
           <t>'+971 6 542 3399</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18690/gopi-medical-clinic</t>
@@ -5766,11 +4978,7 @@
           <t>'+971 6 561 6016</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18695/gulf-ayurvedic-centre</t>
@@ -5793,11 +5001,7 @@
           <t>'+971 2 621 7715</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/239069/gulf-medical-projects-company</t>
@@ -5820,11 +5024,7 @@
           <t>'+971 6 572 7767</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153532/habib-dr-ent-clinic</t>
@@ -5847,11 +5047,7 @@
           <t>'+971 6 559 9234</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18709/hakim-medical-center</t>
@@ -5874,11 +5070,7 @@
           <t>'+971 6 562 5634</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18758/jeena-clinic</t>
@@ -5901,11 +5093,7 @@
           <t>'+971 6 555 1937</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153244/joseph-dental-clinic-dr</t>
@@ -5928,11 +5116,7 @@
           <t>'+971 9 277 7002</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153294/kalba-medical-center</t>
@@ -5955,11 +5139,7 @@
           <t>'+971 6 561 8335</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18779/khalid-polyclinic</t>
@@ -5982,11 +5162,7 @@
           <t>'+971 6 559 9828</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18788/knan-dental-clinic</t>
@@ -6009,11 +5185,7 @@
           <t>'+971 6 543 7388</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/147640/kuwait-danish-dairy-co-kcsc-the</t>
@@ -6036,11 +5208,7 @@
           <t>'+971 6 563 0447</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153362/laika-wali-medical-clinic</t>
@@ -6063,11 +5231,7 @@
           <t>'+971 6 533 3951</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153360/legend-clinic</t>
@@ -6090,11 +5254,7 @@
           <t>'+971 6 561 6464</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153527/mampilly-clinic</t>
@@ -6117,11 +5277,7 @@
           <t>'+971 6 568 5557</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153423/mandar-medical-clinic-dr</t>
@@ -6144,11 +5300,7 @@
           <t>'+971 6 544 0555</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/243414/med-pharma</t>
@@ -6171,11 +5323,7 @@
           <t>'+971 6 572 2999</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153332/metawi-medical-paediatrician-clinic</t>
@@ -6198,11 +5346,7 @@
           <t>'+971 6 556 5656</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153384/mohd-a-el-nounou-clinic-dr</t>
@@ -6225,11 +5369,7 @@
           <t>'+971 6 563 6192</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153730/mohd-tharwat-dental-clinic-dr</t>
@@ -6252,11 +5392,7 @@
           <t>'+971 6 553 8238</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153506/mouen-junblat-medical-centre-dr</t>
@@ -6279,11 +5415,7 @@
           <t>'+971 6 573 6500</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/147666/national-agric-dev-co-the</t>
@@ -6306,11 +5438,7 @@
           <t>'+971 6 562 3834</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153394/nathani-clinic</t>
@@ -6333,11 +5461,7 @@
           <t>'+971 6 523 3300</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/342435/national-center-for-modern-medicine</t>
@@ -6360,11 +5484,7 @@
           <t>'+971 6 568 4974</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18905/noor-clinic</t>
@@ -6387,11 +5507,7 @@
           <t>'+971 6 573 7735</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18911/our-own-medical-and-diagnostics-center</t>
@@ -6414,11 +5530,7 @@
           <t>'+971 6 573 7735</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D223" t="inlineStr"/>
       <c r="E223" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153243/our-own-medicaldiagnostics-center</t>
@@ -6441,11 +5553,7 @@
           <t>'+971 6 557 1797</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D224" t="inlineStr"/>
       <c r="E224" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/246461/pharmacare-limited</t>
@@ -6468,11 +5576,7 @@
           <t>'+971 6 562 5890</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18928/private-eye-clinic</t>
@@ -6495,11 +5599,7 @@
           <t>'+971 6 573 7789</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153370/psychiatric-clinic</t>
@@ -6522,11 +5622,7 @@
           <t>'+971 6 574 4677</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153366/raad-al-qasik-medical-centre-dr</t>
@@ -6549,11 +5645,7 @@
           <t>'+971 6 572 2330</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153348/rania-al-qedrah-specialized-clinic-dr</t>
@@ -6576,11 +5668,7 @@
           <t>'+971 6 562 0831</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153379/reem-medical-diagnostic-centre</t>
@@ -6603,11 +5691,7 @@
           <t>'+971 6 562 5422</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153729/reem-specialists-medical-center</t>
@@ -6630,11 +5714,7 @@
           <t>'+971 6 561 2900</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18950/rishil-poly-clinic</t>
@@ -6657,11 +5737,7 @@
           <t>'+971 6 533 8732</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153324/sadeq-al-sahaf-dr</t>
@@ -6684,11 +5760,7 @@
           <t>'+971 6 567 6027</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18969/sajida-medical-centre</t>
@@ -6711,11 +5783,7 @@
           <t>'+971 6 553 7007</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153248/samir-abu-zied-clinic-dr</t>
@@ -6738,11 +5806,7 @@
           <t>'+971 6 556 5589</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153357/samia-khedr-medical-clinic-dr</t>
@@ -6765,11 +5829,7 @@
           <t>'+971 6 574 2434</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153760/samir-ali-murad-dental-clinic-dr</t>
@@ -6792,11 +5852,7 @@
           <t>'+971 6 562 6525</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153257/sanjay-medical-centre-dr</t>
@@ -6819,11 +5875,7 @@
           <t>'+971 6 568 2670</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18977/sarhad-medical-clinic</t>
@@ -6846,11 +5898,7 @@
           <t>'+971 6 562 6957</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18978/sasils-dental-clinic</t>
@@ -6873,11 +5921,7 @@
           <t>'+971 6 563 6308</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153824/shakir-s-vali-dr</t>
@@ -6900,11 +5944,7 @@
           <t>'+971 6 561 6556</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153335/solanki-dental-centre</t>
@@ -6927,11 +5967,7 @@
           <t>'+971 6 573 7242</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153356/suha-al-farhan-children-dentist-dr</t>
@@ -6954,11 +5990,7 @@
           <t>'+971 6 573 0666</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/19012/swedish-clinic</t>
@@ -6981,11 +6013,7 @@
           <t>'+971 6 533 9196</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/147639/united-dairies</t>
@@ -7008,11 +6036,7 @@
           <t>'+971 6 568 2258</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D245" t="inlineStr"/>
       <c r="E245" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153114/venniyil-clinic</t>
@@ -7035,11 +6059,7 @@
           <t>'+971 6 572 1313</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153351/wassim-kabbani-clinic-dr</t>
@@ -7062,11 +6082,7 @@
           <t>'+971 6 577 1757</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153820/wilson-specialized-hospital</t>
@@ -7089,11 +6105,7 @@
           <t>'+971 6 577 1757</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/19052/w-wilson-health-care-group</t>
@@ -7116,11 +6128,7 @@
           <t>'+971 6 538 8205</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18159/al-maliky-dental-clinic</t>
@@ -7139,11 +6147,7 @@
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/226714/al-riyadh-medical-equipments-centre</t>
@@ -7166,11 +6170,7 @@
           <t>'+971 6 568 5022</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18246/al-shrook-polyclinic</t>
@@ -7189,11 +6189,7 @@
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D252" t="inlineStr"/>
       <c r="E252" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/228491/al-taheal-medical-equipment</t>
@@ -7216,11 +6212,7 @@
           <t>'+971 6 568 7728</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18284/ambegaokar-clinic</t>
@@ -7243,11 +6235,7 @@
           <t>'+971 6 562 0404</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18397/delta-medical-clinic</t>
@@ -7270,11 +6258,7 @@
           <t>'+971 6 573 6466</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18501/dr-labib-al-hasan-medical-clinic</t>
@@ -7297,11 +6281,7 @@
           <t>'+971 6 561 5754</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18730/hyma-medical-clinic</t>
@@ -7324,11 +6304,7 @@
           <t>'+971 6 561 5754</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153325/hyma-medical-clinic-hemalatha-dr</t>
@@ -7347,11 +6323,7 @@
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D258" t="inlineStr"/>
       <c r="E258" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/240124/ibn-rushd-medical-drugs-equipment-store</t>
@@ -7374,11 +6346,7 @@
           <t>'+971 6 573 6466</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153434/labib-al-hasan-medical-clinic-dr</t>
@@ -7401,11 +6369,7 @@
           <t>'+971 6 563 4347</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D260" t="inlineStr"/>
       <c r="E260" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18839/mediplus-diagnostic-centre</t>
@@ -7428,11 +6392,7 @@
           <t>'+971 9 277 7351</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153411/zafar-dental-clinic</t>
@@ -7455,11 +6415,7 @@
           <t>'+971 6 561 4266</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D262" t="inlineStr"/>
       <c r="E262" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18091/al-dallah-medical-clinic</t>
@@ -7482,11 +6438,7 @@
           <t>'+971 6 555 1231</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D263" t="inlineStr"/>
       <c r="E263" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18136/al-jawhara-medical-center</t>
@@ -7509,11 +6461,7 @@
           <t>'+971 6 564 6252</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D264" t="inlineStr"/>
       <c r="E264" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18150/al-lulu-medical-center</t>
@@ -7536,11 +6484,7 @@
           <t>'+971 6 568 6511</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D265" t="inlineStr"/>
       <c r="E265" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18179/al-mushtaq-medical-centre</t>
@@ -7563,11 +6507,7 @@
           <t>'+971 6 538 6444</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D266" t="inlineStr"/>
       <c r="E266" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/17633/al-qassemi-hospital</t>
@@ -7590,11 +6530,7 @@
           <t>'+971 6 568 7893</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D267" t="inlineStr"/>
       <c r="E267" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18209/al-rai-medical-centre</t>
@@ -7617,11 +6553,7 @@
           <t>'+971 6 561 9999</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153809/al-zahra-pvt-hospital</t>
@@ -7644,11 +6576,7 @@
           <t>'+971 6 568 1717</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D269" t="inlineStr"/>
       <c r="E269" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18333/bhatia-clinic</t>
@@ -7671,11 +6599,7 @@
           <t>'+971 6 563 6552</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D270" t="inlineStr"/>
       <c r="E270" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18387/dabbous-medical-centre</t>
@@ -7698,11 +6622,7 @@
           <t>'+971 6 572 5626</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D271" t="inlineStr"/>
       <c r="E271" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18392/davis-dental-clinic</t>
@@ -7725,11 +6645,7 @@
           <t>'+971 6 553 8238</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18532/dr-mouen-junblat-dental-clinic</t>
@@ -7752,11 +6668,7 @@
           <t>'+971 6 574 1313</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18550/dr-oras-sharif-clinic</t>
@@ -7779,11 +6691,7 @@
           <t>'+971 6 572 1919</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18570/dr-said-h-muwafi</t>
@@ -7806,11 +6714,7 @@
           <t>'+971 6 572 2458</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18572/dr-saleh-mohammed-saleh</t>
@@ -7829,11 +6733,7 @@
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/236155/dynamic-rehab-medical-centre</t>
@@ -7856,11 +6756,7 @@
           <t>'+971 6 555 2150</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18650/family-clinic</t>
@@ -7883,11 +6779,7 @@
           <t>'+971 6 561 8300</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18763/jessy-clinic</t>
@@ -7910,11 +6802,7 @@
           <t>'+971 6 561 5307</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18798/lyla-dental-clinic</t>
@@ -7937,11 +6825,7 @@
           <t>'+971 6 568 3405</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18951/rolla-clinic</t>
@@ -7964,11 +6848,7 @@
           <t>'+971 6 563 5201</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18952/romira-paediatric-clinic</t>
@@ -7991,11 +6871,7 @@
           <t>'+971 6 573 6800</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/19006/specialized-medical-center</t>
@@ -8018,11 +6894,7 @@
           <t>'+971 6 572 4484</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18468/dr-gills-clinic</t>
@@ -8041,11 +6913,7 @@
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/218254/al-ameen-medical-centre</t>
@@ -8068,11 +6936,7 @@
           <t>'+971 6 555 1981</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D285" t="inlineStr"/>
       <c r="E285" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/152776/assi-dental-clinic-dr</t>
@@ -8095,11 +6959,7 @@
           <t>'+971 6 538 6444</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D286" t="inlineStr"/>
       <c r="E286" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153808/new-al-qassemiya-hospital</t>
@@ -8122,11 +6982,7 @@
           <t>'+971 6 542 0066</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D287" t="inlineStr"/>
       <c r="E287" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/364526/modern-clinic</t>
@@ -8149,11 +7005,7 @@
           <t>'+971 6 573 3440</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D288" t="inlineStr"/>
       <c r="E288" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153339/abdulla-semrin-clinic-dr</t>
@@ -8176,11 +7028,7 @@
           <t>'+971 6 555 1231</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D289" t="inlineStr"/>
       <c r="E289" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153504/adnan-ballout-clinic-dr</t>
@@ -8203,11 +7051,7 @@
           <t>'+971 6 556 1220</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18036/advanced-eye-clinic</t>
@@ -8230,11 +7074,7 @@
           <t>'+971 6 562 1700</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18059/al-ahlia-regional-medical-centre</t>
@@ -8257,11 +7097,7 @@
           <t>'+971 6 561 5545</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18071/al-amanah-medical-centre</t>
@@ -8284,11 +7120,7 @@
           <t>'+971 6 561 6828</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/152760/al-ansari-clinic</t>
@@ -8311,11 +7143,7 @@
           <t>'+971 6 534 8384</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/302790/al-araimi-gen-trading-llc</t>
@@ -8338,11 +7166,7 @@
           <t>'+971 6 555 9905</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D295" t="inlineStr"/>
       <c r="E295" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/333726/al-alfiah-dental-clinic</t>
@@ -8365,11 +7189,7 @@
           <t>'+971 6 543 1763</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18085/al-barakah-medical-clinic</t>
@@ -8392,11 +7212,7 @@
           <t>'+971 6 543 1763</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/152771/al-baras-al-khaimahah-medical-clinic</t>
@@ -8419,11 +7235,7 @@
           <t>'+971 6 572 7175</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D298" t="inlineStr"/>
       <c r="E298" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153105/al-batool-complex-medical</t>
@@ -8446,11 +7258,7 @@
           <t>'+971 6 533 6176</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18095/al-darary-medical-centre</t>
@@ -8473,11 +7281,7 @@
           <t>'+971 6 532 0800</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153731/al-diyafah-medical-centre</t>
@@ -8500,11 +7304,7 @@
           <t>'+971 6 534 3870</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/331951/al-fanar-food-industries-llc</t>
@@ -8527,11 +7327,7 @@
           <t>'+971 6 556 2444</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/152778/al-huda-polyclinic</t>
@@ -8554,11 +7350,7 @@
           <t>'+971 6 561 3613</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18128/al-ishraf-medical-centre</t>
@@ -8581,11 +7373,7 @@
           <t>'+971 6 561 3613</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153305/al-ishraf-medical-center</t>
@@ -8608,11 +7396,7 @@
           <t>'+971 6 556 5660</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18156/al-majaz-medical-centre</t>
@@ -8635,11 +7419,7 @@
           <t>'+971 6 573 9545</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18176/al-muntasir-medical-centre</t>
@@ -8662,11 +7442,7 @@
           <t>'+971 6 538 8205</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D307" t="inlineStr"/>
       <c r="E307" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18160/al-maliky-dental-clinic</t>
@@ -8689,11 +7465,7 @@
           <t>'+971 4 338 3339</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D308" t="inlineStr"/>
       <c r="E308" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/224696/al-mufid-trading-company-llc</t>
@@ -8716,11 +7488,7 @@
           <t>'+971 6 561 8899</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18185/al-nakheel-medical-centre</t>
@@ -8743,11 +7511,7 @@
           <t>'+971 6 561 2696</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18181/al-naeem-medical-center</t>
@@ -8770,11 +7534,7 @@
           <t>'+971 6 533 4415</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18204/al-raha-medical-center</t>
@@ -8797,11 +7557,7 @@
           <t>'+971 6 533 3913</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/318786/al-rubiyan-trading-company-llc</t>
@@ -8824,11 +7580,7 @@
           <t>'+971 6 557 5075</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/332063/al-rimal-foodstuff-inds-fzc</t>
@@ -8851,11 +7603,7 @@
           <t>'+971 6 562 3949</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18218/al-saadah-medical-center</t>
@@ -8878,11 +7626,7 @@
           <t>'+971 6 563 5211</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18219/al-safa-clinic</t>
@@ -8905,11 +7649,7 @@
           <t>'+971 6 563 2618</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18223/al-saha-wa-al-shifaa-specialities-complex</t>
@@ -8932,11 +7672,7 @@
           <t>'+971 6 532 5327</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/148788/al-shams-food-industries</t>
@@ -8959,11 +7695,7 @@
           <t>'+971(6)379735</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/299592/al-shulla-vet-center</t>
@@ -8986,11 +7718,7 @@
           <t>'+971 6 563 2618</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/333639/al-soha-and-al-shifa-specialities-complex</t>
@@ -9013,11 +7741,7 @@
           <t>'+971 6 572 7757</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153338/al-thequah-clinic</t>
@@ -9040,11 +7764,7 @@
           <t>'+971 6 534 7494</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D321" t="inlineStr"/>
       <c r="E321" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18259/al-wafir-medical-centre</t>
@@ -9067,11 +7787,7 @@
           <t>'+971 6 574 9666</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D322" t="inlineStr"/>
       <c r="E322" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18266/al-widad-specialist-clinic</t>
@@ -9094,11 +7810,7 @@
           <t>'+971 6 574 9666</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/333683/al-widad-specialist</t>
@@ -9121,11 +7833,7 @@
           <t>'+971 6 561 9999</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D324" t="inlineStr"/>
       <c r="E324" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/299495/al-zahar-hospital</t>
@@ -9148,11 +7856,7 @@
           <t>'+971 6 556 5564</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D325" t="inlineStr"/>
       <c r="E325" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18282/amal-abdel-kader-dental-clinic</t>
@@ -9175,11 +7879,7 @@
           <t>'+971 6 563 0555</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D326" t="inlineStr"/>
       <c r="E326" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18299/anthony-medical-centre</t>
@@ -9202,11 +7902,7 @@
           <t>'+971 6 563 0555</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/152770/antony-medical-centre</t>
@@ -9229,11 +7925,7 @@
           <t>'+971 6 538 7199</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18301/apollo-medical-clinic</t>
@@ -9256,11 +7948,7 @@
           <t>'+971 6 574 8290</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/232623/baniyas-medical-equipment-trading</t>
@@ -9283,11 +7971,7 @@
           <t>'+971 6 532 8558</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/333644/bilal-medical-centre</t>
@@ -9310,11 +7994,7 @@
           <t>'+971 6 562 0181</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153272/chithra-shamsudheens-clinic-dr</t>
@@ -9337,11 +8017,7 @@
           <t>'+971 6 568 5466</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153734/chinese-clinic-the</t>
@@ -9364,11 +8040,7 @@
           <t>'+971 6 524 3444</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18372/cocoon-individualized-natal-care</t>
@@ -9391,11 +8063,7 @@
           <t>'+971 6 533 5555</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18376/consultant-polymedic</t>
@@ -9418,11 +8086,7 @@
           <t>'+971 6 561 8801</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/333736/derma-health</t>
@@ -9445,11 +8109,7 @@
           <t>'+971 6 558 4335</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18408/deva-medical-centre</t>
@@ -9472,11 +8132,7 @@
           <t>'+971 6 562 0181</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D337" t="inlineStr"/>
       <c r="E337" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18453/dr-chithra-shamsudheens-clinic</t>
@@ -9499,11 +8155,7 @@
           <t>'+971 6 561 6261</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18506/dr-maged-salah-eldin</t>
@@ -9526,11 +8178,7 @@
           <t>'+971 6 573 9899</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18515/dr-mariyam-dental-clinic</t>
@@ -9553,11 +8201,7 @@
           <t>'+971 6 555 2116</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18525/dr-mohd-ahmed-ali-dental-clinic</t>
@@ -9580,11 +8224,7 @@
           <t>'+971 6 556 5568</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18551/dr-rabha-habib-el-sayegh-clinic</t>
@@ -9607,11 +8247,7 @@
           <t>'+971 6 569 0569</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/18558/dr-ravindran-gopal-clinic</t>
@@ -9634,11 +8270,7 @@
           <t>'+971 6 555 1666</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/152775/emirates-pvt-poly-clinic</t>
@@ -9661,11 +8293,7 @@
           <t>'+971 6 573 6866</t>
         </is>
       </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/236644/emirates-medical-lab</t>
@@ -9688,11 +8316,7 @@
           <t>'+971 6 556 3433</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/333741/enjab-hospital-for-day-care</t>
@@ -9715,11 +8339,7 @@
           <t>'+971 6 556 0002</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D346" t="inlineStr"/>
       <c r="E346" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153409/ent-specialized-clinic</t>
@@ -9742,11 +8362,7 @@
           <t>'+971 6 559 1110</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D347" t="inlineStr"/>
       <c r="E347" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153112/gayatree-medical-centre</t>
@@ -9769,11 +8385,7 @@
           <t>'+971 6 568 5620</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D348" t="inlineStr"/>
       <c r="E348" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153117/hayat-medical-centre</t>
@@ -9796,11 +8408,7 @@
           <t>'+971 6 563 5029</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D349" t="inlineStr"/>
       <c r="E349" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153308/hejazis-clinic-dr</t>
@@ -9823,11 +8431,7 @@
           <t>'+971 6 568 7000</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D350" t="inlineStr"/>
       <c r="E350" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153438/islamic-medical-herbs-treatment-center</t>
@@ -9850,11 +8454,7 @@
           <t>'+971 6 568 7255</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D351" t="inlineStr"/>
       <c r="E351" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/240841/ismail-mohd-al-nimir</t>
@@ -9877,11 +8477,7 @@
           <t>'+971 6 572 4855</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D352" t="inlineStr"/>
       <c r="E352" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153361/jwan-s-murad-clinic-dr</t>
@@ -9904,11 +8500,7 @@
           <t>'+971 6 562 4725</t>
         </is>
       </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153249/kottakkal-health-massage</t>
@@ -9931,11 +8523,7 @@
           <t>'+971 6 561 6261</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153746/maged-salah-el-din-clinic-dr</t>
@@ -9958,11 +8546,7 @@
           <t>'+971 6 572 6272</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153371/malek-a-nawas-dr</t>
@@ -9985,11 +8569,7 @@
           <t>'+971 6 572 6272</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153387/malek-abdulla-nawas-dr</t>
@@ -10012,11 +8592,7 @@
           <t>'+971 6 568 5557</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/333664/mandar-medical-centre</t>
@@ -10039,11 +8615,7 @@
           <t>'+971 6 573 9899</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D358" t="inlineStr"/>
       <c r="E358" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153262/mariyam-dental-clinic-dr</t>
@@ -10066,11 +8638,7 @@
           <t>'+971 6 572 2999</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D359" t="inlineStr"/>
       <c r="E359" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153381/metawi-medical-clinic</t>
@@ -10093,11 +8661,7 @@
           <t>'+971 6 574 9610</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D360" t="inlineStr"/>
       <c r="E360" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/333734/minal-specialised-clinic-dermatology</t>
@@ -10120,11 +8684,7 @@
           <t>'+971 6 555 2116</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D361" t="inlineStr"/>
       <c r="E361" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153510/mohd-ahamad-ali-dental-clinic-dr</t>
@@ -10147,11 +8707,7 @@
           <t>'+971 6 561 7755</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D362" t="inlineStr"/>
       <c r="E362" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/153331/mount-seena-medical-centre</t>
@@ -10174,11 +8730,7 @@
           <t>'+971(6)384166</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D363" t="inlineStr"/>
       <c r="E363" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/299599/nadd-al-shiba-vet-clinic</t>
@@ -10201,11 +8753,7 @@
           <t>'+971 6 534 6522</t>
         </is>
       </c>
-      <c r="D364" t="inlineStr">
-        <is>
-          <t>kiwavix919@dwseal.co</t>
-        </is>
-      </c>
+      <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr">
         <is>
           <t>https://www.yello.ae/company/333669/nanda-medical-centre</t>
